--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_BAXI Manresa.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_BAXI Manresa.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2226.64</v>
+        <v>2559.12</v>
       </c>
       <c r="C2" t="n">
-        <v>2229.54</v>
+        <v>2562.88</v>
       </c>
       <c r="D2" t="n">
-        <v>106.4345111547673</v>
+        <v>107.3401797977276</v>
       </c>
       <c r="E2" t="n">
-        <v>114.3733684975376</v>
+        <v>113.6611936571357</v>
       </c>
       <c r="F2" t="n">
-        <v>0.511001100110011</v>
+        <v>0.5146212847555129</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1697613148072641</v>
+        <v>0.1693863918312816</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3074003795066413</v>
+        <v>0.3101736972704714</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2832783278327833</v>
+        <v>0.2895493767976989</v>
       </c>
       <c r="J2" t="n">
-        <v>315</v>
+        <v>373</v>
       </c>
       <c r="K2" t="n">
-        <v>331</v>
+        <v>382</v>
       </c>
       <c r="L2" t="n">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="M2" t="n">
-        <v>411</v>
+        <v>466</v>
       </c>
       <c r="N2" t="n">
-        <v>871</v>
+        <v>1005</v>
       </c>
       <c r="O2" t="n">
-        <v>1200</v>
+        <v>1379</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6600660066006601</v>
+        <v>0.6610738255033557</v>
       </c>
       <c r="Q2" t="n">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="R2" t="n">
-        <v>320</v>
+        <v>378</v>
       </c>
       <c r="S2" t="n">
-        <v>0.176017601760176</v>
+        <v>0.1812080536912752</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="U2" t="n">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1056105610561056</v>
+        <v>0.1045062320230105</v>
       </c>
       <c r="W2" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="X2" t="n">
-        <v>198</v>
+        <v>240</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1089108910891089</v>
+        <v>0.1150527325023969</v>
       </c>
       <c r="Z2" t="n">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="AA2" t="n">
-        <v>589</v>
+        <v>669</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.323982398239824</v>
+        <v>0.3207094918504315</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7258333333333333</v>
+        <v>0.728788977519942</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3375</v>
+        <v>0.3439153439153439</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3125</v>
+        <v>0.3211009174311927</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3535353535353535</v>
+        <v>0.35</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3395585738539898</v>
+        <v>0.3452914798206278</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.451666666666667</v>
+        <v>1.457577955039884</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.625</v>
+        <v>0.6422018348623854</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.029224904701398</v>
+        <v>1.03960396039604</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.7415506958250497</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.021604938271605</v>
+        <v>1.018666666666667</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.663934426229508</v>
+        <v>1.636986301369863</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.150115473441109</v>
+        <v>1.146881287726358</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.198614318706698</v>
+        <v>4.197183098591549</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.348729792147806</v>
+        <v>5.344064386317908</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79.52285714285713</v>
+        <v>79.9725</v>
       </c>
       <c r="C3" t="n">
-        <v>79.62642857142858</v>
+        <v>80.09</v>
       </c>
       <c r="D3" t="n">
-        <v>106.4345111547673</v>
+        <v>107.3401797977276</v>
       </c>
       <c r="E3" t="n">
-        <v>114.3733684975376</v>
+        <v>113.6611936571357</v>
       </c>
       <c r="F3" t="n">
-        <v>0.511001100110011</v>
+        <v>0.5146212847555129</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1697613148072641</v>
+        <v>0.1693863918312816</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3074003795066413</v>
+        <v>0.3101736972704714</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2832783278327833</v>
+        <v>0.2895493767976989</v>
       </c>
       <c r="J3" t="n">
-        <v>11.25</v>
+        <v>11.65625</v>
       </c>
       <c r="K3" t="n">
-        <v>11.82142857142857</v>
+        <v>11.9375</v>
       </c>
       <c r="L3" t="n">
-        <v>7.25</v>
+        <v>7.46875</v>
       </c>
       <c r="M3" t="n">
-        <v>14.67857142857143</v>
+        <v>14.5625</v>
       </c>
       <c r="N3" t="n">
-        <v>31.10714285714286</v>
+        <v>31.40625</v>
       </c>
       <c r="O3" t="n">
-        <v>42.85714285714285</v>
+        <v>43.09375</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6600660066006599</v>
+        <v>0.6610738255033557</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.857142857142857</v>
+        <v>4.0625</v>
       </c>
       <c r="R3" t="n">
-        <v>11.42857142857143</v>
+        <v>11.8125</v>
       </c>
       <c r="S3" t="n">
-        <v>0.176017601760176</v>
+        <v>0.1812080536912752</v>
       </c>
       <c r="T3" t="n">
-        <v>2.142857142857143</v>
+        <v>2.1875</v>
       </c>
       <c r="U3" t="n">
-        <v>6.857142857142857</v>
+        <v>6.8125</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1056105610561056</v>
+        <v>0.1045062320230105</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5</v>
+        <v>2.625</v>
       </c>
       <c r="X3" t="n">
-        <v>7.071428571428571</v>
+        <v>7.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1089108910891089</v>
+        <v>0.1150527325023969</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.142857142857143</v>
+        <v>7.21875</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.03571428571428</v>
+        <v>20.90625</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3239823982398239</v>
+        <v>0.3207094918504315</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7258333333333334</v>
+        <v>0.728788977519942</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3375</v>
+        <v>0.3439153439153439</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3125</v>
+        <v>0.3211009174311927</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3535353535353535</v>
+        <v>0.35</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3395585738539899</v>
+        <v>0.3452914798206278</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.451666666666667</v>
+        <v>1.457577955039884</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.625</v>
+        <v>0.6422018348623854</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.029224904701398</v>
+        <v>1.03960396039604</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.7415506958250497</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.021604938271605</v>
+        <v>1.018666666666667</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.663934426229508</v>
+        <v>1.636986301369863</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.150115473441109</v>
+        <v>1.146881287726358</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.198614318706698</v>
+        <v>4.197183098591549</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.348729792147807</v>
+        <v>5.344064386317908</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2232.440000000001</v>
+        <v>2566.640000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>2229.54</v>
+        <v>2562.88</v>
       </c>
       <c r="D4" t="n">
-        <v>114.3733684975376</v>
+        <v>113.6611936571357</v>
       </c>
       <c r="E4" t="n">
-        <v>106.4345111547673</v>
+        <v>107.3401797977276</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5428875865743207</v>
+        <v>0.5404651162790698</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1667024342387639</v>
+        <v>0.1678546638902237</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3653100775193798</v>
+        <v>0.3622577927548442</v>
       </c>
       <c r="I4" t="n">
-        <v>0.272775705913692</v>
+        <v>0.273953488372093</v>
       </c>
       <c r="J4" t="n">
-        <v>348</v>
+        <v>381</v>
       </c>
       <c r="K4" t="n">
-        <v>372</v>
+        <v>422</v>
       </c>
       <c r="L4" t="n">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="M4" t="n">
-        <v>402</v>
+        <v>467</v>
       </c>
       <c r="N4" t="n">
-        <v>974</v>
+        <v>1115</v>
       </c>
       <c r="O4" t="n">
-        <v>1372</v>
+        <v>1561</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7309536494405967</v>
+        <v>0.726046511627907</v>
       </c>
       <c r="Q4" t="n">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="R4" t="n">
-        <v>288</v>
+        <v>335</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1534363345764518</v>
+        <v>0.1558139534883721</v>
       </c>
       <c r="T4" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="U4" t="n">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1028236547682472</v>
+        <v>0.1051162790697674</v>
       </c>
       <c r="W4" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="X4" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06712839637719765</v>
+        <v>0.0641860465116279</v>
       </c>
       <c r="Z4" t="n">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="AA4" t="n">
-        <v>574</v>
+        <v>671</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3058071390516782</v>
+        <v>0.312093023255814</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7099125364431487</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3784722222222222</v>
+        <v>0.382089552238806</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.4093264248704663</v>
+        <v>0.3761061946902655</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3968253968253968</v>
+        <v>0.4057971014492754</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3368107302533532</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.419825072886297</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.8186528497409327</v>
+        <v>0.7522123893805309</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.054285714285714</v>
+        <v>1.045735475896168</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8036951501154734</v>
+        <v>0.7665995975855131</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.986737400530504</v>
+        <v>0.9813953488372092</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.565217391304348</v>
+        <v>1.596491228070176</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.032183908045977</v>
+        <v>1.011928429423459</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.314942528735632</v>
+        <v>4.274353876739562</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.347126436781609</v>
+        <v>5.286282306163022</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.73000000000002</v>
+        <v>80.20750000000002</v>
       </c>
       <c r="C5" t="n">
-        <v>79.62642857142858</v>
+        <v>80.09</v>
       </c>
       <c r="D5" t="n">
-        <v>114.3733684975376</v>
+        <v>113.6611936571357</v>
       </c>
       <c r="E5" t="n">
-        <v>106.4345111547673</v>
+        <v>107.3401797977276</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5428875865743208</v>
+        <v>0.5404651162790698</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1667024342387639</v>
+        <v>0.1678546638902237</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3653100775193798</v>
+        <v>0.3622577927548442</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2727757059136921</v>
+        <v>0.273953488372093</v>
       </c>
       <c r="J5" t="n">
-        <v>12.42857142857143</v>
+        <v>11.90625</v>
       </c>
       <c r="K5" t="n">
-        <v>13.28571428571429</v>
+        <v>13.1875</v>
       </c>
       <c r="L5" t="n">
-        <v>5.142857142857143</v>
+        <v>5.6875</v>
       </c>
       <c r="M5" t="n">
-        <v>14.35714285714286</v>
+        <v>14.59375</v>
       </c>
       <c r="N5" t="n">
-        <v>34.78571428571428</v>
+        <v>34.84375</v>
       </c>
       <c r="O5" t="n">
-        <v>49</v>
+        <v>48.78125</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7309536494405968</v>
+        <v>0.726046511627907</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.892857142857143</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>10.28571428571429</v>
+        <v>10.46875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1534363345764518</v>
+        <v>0.1558139534883721</v>
       </c>
       <c r="T5" t="n">
-        <v>2.821428571428572</v>
+        <v>2.65625</v>
       </c>
       <c r="U5" t="n">
-        <v>6.892857142857143</v>
+        <v>7.0625</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1028236547682472</v>
+        <v>0.1051162790697674</v>
       </c>
       <c r="W5" t="n">
-        <v>1.785714285714286</v>
+        <v>1.75</v>
       </c>
       <c r="X5" t="n">
-        <v>4.5</v>
+        <v>4.3125</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06712839637719767</v>
+        <v>0.0641860465116279</v>
       </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>7.0625</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.5</v>
+        <v>20.96875</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3058071390516782</v>
+        <v>0.312093023255814</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7099125364431487</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3784722222222222</v>
+        <v>0.382089552238806</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.4093264248704663</v>
+        <v>0.3761061946902655</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3968253968253969</v>
+        <v>0.4057971014492754</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3368107302533532</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.419825072886297</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.8186528497409327</v>
+        <v>0.7522123893805309</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.054285714285714</v>
+        <v>1.045735475896168</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8036951501154735</v>
+        <v>0.7665995975855131</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.9867374005305041</v>
+        <v>0.9813953488372092</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.565217391304348</v>
+        <v>1.596491228070176</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.032183908045977</v>
+        <v>1.011928429423459</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.314942528735632</v>
+        <v>4.274353876739562</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.347126436781608</v>
+        <v>5.286282306163022</v>
       </c>
     </row>
     <row r="7">
@@ -1419,16 +1419,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D8" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1437,49 +1437,49 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I8" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J8" t="n">
         <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L8" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M8" t="n">
         <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R8" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="S8" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="T8" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="U8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W8" t="n">
         <v>2</v>
@@ -1488,10 +1488,10 @@
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="Z8" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="AA8" t="n">
         <v>0.772</v>
@@ -1534,41 +1534,41 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>392:51</t>
+          <t>442:42</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>104.76</v>
+        <v>112.4</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.873</v>
+        <v>0.879</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.824</v>
+        <v>0.828</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.365</v>
+        <v>1.361</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.172</v>
+        <v>0.178</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.524</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.556</v>
+        <v>0.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.118</v>
+        <v>0.111</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.076</v>
+        <v>0.074</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.111</v>
+        <v>0.112</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="9">
@@ -1718,16 +1718,16 @@
         <v>2.31</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.272</v>
+        <v>0.27</v>
       </c>
       <c r="AW9" t="n">
         <v>0.041</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.092</v>
+        <v>0.091</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.091</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="10">
@@ -1737,156 +1737,156 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>56</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" t="n">
+        <v>22</v>
+      </c>
+      <c r="F10" t="n">
         <v>4</v>
       </c>
-      <c r="C10" t="n">
-        <v>34</v>
-      </c>
-      <c r="D10" t="n">
-        <v>8</v>
-      </c>
-      <c r="E10" t="n">
-        <v>16</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
       <c r="G10" t="n">
+        <v>26</v>
+      </c>
+      <c r="H10" t="n">
+        <v>22</v>
+      </c>
+      <c r="I10" t="n">
+        <v>28</v>
+      </c>
+      <c r="J10" t="n">
+        <v>15</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>14</v>
       </c>
-      <c r="H10" t="n">
-        <v>15</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="Q10" t="n">
+        <v>14</v>
+      </c>
+      <c r="R10" t="n">
         <v>18</v>
       </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>13</v>
-      </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="T10" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="U10" t="n">
         <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="Z10" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.778</v>
+        <v>0.725</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.125</v>
+        <v>0.154</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>82:18</t>
+          <t>138:11</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>44.92</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.317</v>
+        <v>0.354</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.448</v>
+        <v>0.464</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.757</v>
+        <v>0.753</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.156</v>
+        <v>0.188</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.5</v>
+        <v>0.458</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.429</v>
+        <v>1.071</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.241</v>
+        <v>0.236</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.065</v>
+        <v>0.077</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.079</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.004</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="11">
@@ -2036,16 +2036,16 @@
         <v>3.333</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.118</v>
+        <v>0.117</v>
       </c>
       <c r="AW11" t="n">
         <v>0.052</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="12">
@@ -2055,40 +2055,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="D12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="F12" t="n">
+        <v>45</v>
+      </c>
+      <c r="G12" t="n">
+        <v>130</v>
+      </c>
+      <c r="H12" t="n">
         <v>33</v>
       </c>
-      <c r="G12" t="n">
-        <v>103</v>
-      </c>
-      <c r="H12" t="n">
-        <v>25</v>
-      </c>
       <c r="I12" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="J12" t="n">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="K12" t="n">
+        <v>26</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M12" t="n">
         <v>23</v>
-      </c>
-      <c r="L12" t="n">
-        <v>7</v>
-      </c>
-      <c r="M12" t="n">
-        <v>18</v>
       </c>
       <c r="N12" t="n">
         <v>5</v>
@@ -2097,114 +2097,114 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Q12" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="R12" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="S12" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="T12" t="n">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c r="U12" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="V12" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="W12" t="n">
+        <v>19</v>
+      </c>
+      <c r="X12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>76</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="AB12" t="n">
         <v>14</v>
       </c>
-      <c r="X12" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>38</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>62</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>8</v>
-      </c>
       <c r="AC12" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.381</v>
+        <v>0.412</v>
       </c>
       <c r="AE12" t="n">
         <v>3</v>
       </c>
       <c r="AF12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AI12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.333</v>
+        <v>0.364</v>
       </c>
       <c r="AK12" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="AL12" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.318</v>
+        <v>0.343</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>385:58</t>
+          <t>471:28</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>225.52</v>
+        <v>283.36</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.454</v>
+        <v>0.478</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.487</v>
+        <v>0.51</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.763</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.217</v>
+        <v>0.205</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.154</v>
+        <v>0.16</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.388</v>
+        <v>2.362</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.258</v>
+        <v>0.263</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.159</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="13">
@@ -2214,40 +2214,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>366</v>
+        <v>421</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E13" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F13" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="G13" t="n">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="H13" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I13" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="J13" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K13" t="n">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="L13" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M13" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="N13" t="n">
         <v>6</v>
@@ -2256,114 +2256,114 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Q13" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="S13" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="T13" t="n">
-        <v>366</v>
+        <v>428</v>
       </c>
       <c r="U13" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V13" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="W13" t="n">
+        <v>35</v>
+      </c>
+      <c r="X13" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>106</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>137</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF13" t="n">
         <v>33</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AG13" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="AH13" t="n">
         <v>18</v>
       </c>
-      <c r="Y13" t="n">
-        <v>95</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>125</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>13</v>
-      </c>
       <c r="AI13" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.371</v>
+        <v>0.367</v>
       </c>
       <c r="AK13" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AL13" t="n">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.432</v>
+        <v>0.423</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>684:41</t>
+          <t>781:08</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>324.04</v>
+        <v>373</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.578</v>
+        <v>0.576</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.62</v>
+        <v>0.617</v>
       </c>
       <c r="AR13" t="n">
         <v>1.129</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.089</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.278</v>
+        <v>0.266</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.655</v>
+        <v>0.75</v>
       </c>
       <c r="AV13" t="n">
         <v>0.209</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="14">
@@ -2373,156 +2373,156 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C14" t="n">
-        <v>228</v>
+        <v>278</v>
       </c>
       <c r="D14" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E14" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="F14" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="H14" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="I14" t="n">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="J14" t="n">
+        <v>32</v>
+      </c>
+      <c r="K14" t="n">
+        <v>79</v>
+      </c>
+      <c r="L14" t="n">
+        <v>21</v>
+      </c>
+      <c r="M14" t="n">
+        <v>22</v>
+      </c>
+      <c r="N14" t="n">
+        <v>19</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>51</v>
+      </c>
+      <c r="R14" t="n">
+        <v>43</v>
+      </c>
+      <c r="S14" t="n">
+        <v>106</v>
+      </c>
+      <c r="T14" t="n">
+        <v>332</v>
+      </c>
+      <c r="U14" t="n">
+        <v>41</v>
+      </c>
+      <c r="V14" t="n">
         <v>31</v>
       </c>
-      <c r="K14" t="n">
-        <v>68</v>
-      </c>
-      <c r="L14" t="n">
-        <v>16</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="W14" t="n">
+        <v>36</v>
+      </c>
+      <c r="X14" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>128</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>166</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF14" t="n">
         <v>19</v>
       </c>
-      <c r="N14" t="n">
-        <v>17</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>46</v>
-      </c>
-      <c r="R14" t="n">
-        <v>38</v>
-      </c>
-      <c r="S14" t="n">
-        <v>90</v>
-      </c>
-      <c r="T14" t="n">
-        <v>270</v>
-      </c>
-      <c r="U14" t="n">
-        <v>38</v>
-      </c>
-      <c r="V14" t="n">
-        <v>25</v>
-      </c>
-      <c r="W14" t="n">
-        <v>30</v>
-      </c>
-      <c r="X14" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>104</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>138</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.754</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>16</v>
-      </c>
       <c r="AG14" t="n">
-        <v>0.438</v>
+        <v>0.421</v>
       </c>
       <c r="AH14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI14" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.4</v>
+        <v>0.421</v>
       </c>
       <c r="AK14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL14" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.25</v>
+        <v>0.259</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>490:40</t>
+          <t>566:13</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>255.08</v>
+        <v>295.88</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.457</v>
+        <v>0.48</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.545</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.894</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.18</v>
+        <v>0.172</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.405</v>
+        <v>0.43</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.674</v>
+        <v>0.627</v>
       </c>
       <c r="AV14" t="n">
         <v>0.229</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.035</v>
+        <v>0.039</v>
       </c>
       <c r="AX14" t="n">
         <v>0.151</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.043</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="15">
@@ -2532,22 +2532,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C15" t="n">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G15" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="H15" t="n">
         <v>21</v>
@@ -2559,129 +2559,129 @@
         <v>25</v>
       </c>
       <c r="K15" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R15" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="S15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T15" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="U15" t="n">
         <v>11</v>
       </c>
       <c r="V15" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="W15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Z15" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="AB15" t="n">
         <v>5</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.455</v>
+        <v>0.312</v>
       </c>
       <c r="AE15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="AH15" t="n">
         <v>18</v>
       </c>
       <c r="AI15" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.36</v>
+        <v>0.346</v>
       </c>
       <c r="AK15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AL15" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.356</v>
+        <v>0.366</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>583:44</t>
+          <t>652:06</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>184.88</v>
+        <v>209.88</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.528</v>
+        <v>0.519</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.553</v>
+        <v>0.542</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.022</v>
+        <v>0.996</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.076</v>
+        <v>0.081</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.132</v>
+        <v>0.116</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.786</v>
+        <v>1.471</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.14</v>
+        <v>0.141</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.049</v>
+        <v>0.047</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.08</v>
+        <v>0.081</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="16">
@@ -2691,67 +2691,67 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D16" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
+        <v>22</v>
+      </c>
+      <c r="H16" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" t="n">
         <v>17</v>
       </c>
-      <c r="H16" t="n">
-        <v>6</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>11</v>
       </c>
-      <c r="J16" t="n">
-        <v>6</v>
-      </c>
       <c r="K16" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="L16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M16" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N16" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R16" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="U16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V16" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="W16" t="n">
         <v>8</v>
@@ -2760,87 +2760,87 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Z16" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.654</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC16" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.182</v>
+        <v>0.312</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG16" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1</v>
       </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
       <c r="AI16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL16" t="n">
         <v>9</v>
       </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>8</v>
-      </c>
       <c r="AM16" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>250:25</t>
+          <t>333:23</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>76.84</v>
+        <v>100.48</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.483</v>
+        <v>0.487</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.494</v>
+        <v>0.503</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.833</v>
+        <v>0.836</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.156</v>
+        <v>0.169</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.1</v>
+        <v>0.132</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.5</v>
+        <v>0.647</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.135</v>
+        <v>0.132</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.06</v>
+        <v>0.054</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.122</v>
+        <v>0.153</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="17">
@@ -2850,43 +2850,43 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="D17" t="n">
+        <v>36</v>
+      </c>
+      <c r="E17" t="n">
+        <v>68</v>
+      </c>
+      <c r="F17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G17" t="n">
+        <v>63</v>
+      </c>
+      <c r="H17" t="n">
         <v>31</v>
       </c>
-      <c r="E17" t="n">
-        <v>59</v>
-      </c>
-      <c r="F17" t="n">
-        <v>25</v>
-      </c>
-      <c r="G17" t="n">
-        <v>61</v>
-      </c>
-      <c r="H17" t="n">
-        <v>27</v>
-      </c>
       <c r="I17" t="n">
+        <v>47</v>
+      </c>
+      <c r="J17" t="n">
+        <v>16</v>
+      </c>
+      <c r="K17" t="n">
+        <v>58</v>
+      </c>
+      <c r="L17" t="n">
         <v>40</v>
-      </c>
-      <c r="J17" t="n">
-        <v>15</v>
-      </c>
-      <c r="K17" t="n">
-        <v>52</v>
-      </c>
-      <c r="L17" t="n">
-        <v>38</v>
       </c>
       <c r="M17" t="n">
         <v>18</v>
       </c>
       <c r="N17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2898,31 +2898,31 @@
         <v>28</v>
       </c>
       <c r="R17" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S17" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="T17" t="n">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="U17" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="V17" t="n">
         <v>27</v>
       </c>
       <c r="W17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="X17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y17" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="Z17" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="AA17" t="n">
         <v>0.697</v>
@@ -2931,19 +2931,19 @@
         <v>4</v>
       </c>
       <c r="AC17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.235</v>
+        <v>0.211</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AH17" t="n">
         <v>12</v>
@@ -2955,51 +2955,51 @@
         <v>0.545</v>
       </c>
       <c r="AK17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL17" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.333</v>
+        <v>0.341</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>466:36</t>
+          <t>493:49</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>165.6</v>
+        <v>179.68</v>
       </c>
       <c r="AP17" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="AU17" t="n">
         <v>0.571</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>0.596</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0.169</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0.536</v>
-      </c>
       <c r="AV17" t="n">
-        <v>0.157</v>
+        <v>0.159</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.121</v>
+        <v>0.127</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="18">
@@ -3009,16 +3009,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -3039,7 +3039,7 @@
         <v>5</v>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -3057,7 +3057,7 @@
         <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S18" t="n">
         <v>7</v>
@@ -3087,13 +3087,13 @@
         <v>0.632</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3124,38 +3124,38 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>54:06</t>
+          <t>57:13</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>21.72</v>
+        <v>23.72</v>
       </c>
       <c r="AP18" t="n">
         <v>0.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.541</v>
+        <v>0.536</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.783</v>
+        <v>0.801</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.276</v>
+        <v>0.253</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.7</v>
+        <v>0.583</v>
       </c>
       <c r="AU18" t="n">
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.177</v>
+        <v>0.182</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.079</v>
+        <v>0.093</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.101</v>
+        <v>0.095</v>
       </c>
       <c r="AY18" t="n">
         <v>0</v>
@@ -3168,22 +3168,22 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>15</v>
+      </c>
+      <c r="C19" t="n">
+        <v>135</v>
+      </c>
+      <c r="D19" t="n">
+        <v>31</v>
+      </c>
+      <c r="E19" t="n">
+        <v>62</v>
+      </c>
+      <c r="F19" t="n">
         <v>14</v>
       </c>
-      <c r="C19" t="n">
-        <v>127</v>
-      </c>
-      <c r="D19" t="n">
-        <v>30</v>
-      </c>
-      <c r="E19" t="n">
-        <v>60</v>
-      </c>
-      <c r="F19" t="n">
-        <v>12</v>
-      </c>
       <c r="G19" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H19" t="n">
         <v>31</v>
@@ -3192,16 +3192,16 @@
         <v>38</v>
       </c>
       <c r="J19" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M19" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N19" t="n">
         <v>3</v>
@@ -3210,22 +3210,22 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S19" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="T19" t="n">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="U19" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="V19" t="n">
         <v>16</v>
@@ -3237,22 +3237,22 @@
         <v>6</v>
       </c>
       <c r="Y19" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Z19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.754</v>
+        <v>0.758</v>
       </c>
       <c r="AB19" t="n">
         <v>11</v>
       </c>
       <c r="AC19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.458</v>
+        <v>0.44</v>
       </c>
       <c r="AE19" t="n">
         <v>4</v>
@@ -3264,60 +3264,60 @@
         <v>0.308</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="AK19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.323</v>
+        <v>0.344</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>285:31</t>
+          <t>304:04</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>137.72</v>
+        <v>144.72</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.49</v>
+        <v>0.505</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.554</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.922</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.167</v>
+        <v>0.173</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.316</v>
+        <v>0.301</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.739</v>
+        <v>1.76</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.213</v>
+        <v>0.208</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.037</v>
+        <v>0.038</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.107</v>
+        <v>0.103</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.053</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="20">
@@ -3327,100 +3327,100 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C20" t="n">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E20" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F20" t="n">
         <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H20" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="I20" t="n">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="J20" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K20" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="L20" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="M20" t="n">
         <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q20" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R20" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="S20" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="T20" t="n">
-        <v>285</v>
+        <v>328</v>
       </c>
       <c r="U20" t="n">
+        <v>25</v>
+      </c>
+      <c r="V20" t="n">
+        <v>41</v>
+      </c>
+      <c r="W20" t="n">
+        <v>22</v>
+      </c>
+      <c r="X20" t="n">
         <v>18</v>
       </c>
-      <c r="V20" t="n">
-        <v>32</v>
-      </c>
-      <c r="W20" t="n">
-        <v>20</v>
-      </c>
-      <c r="X20" t="n">
-        <v>16</v>
-      </c>
       <c r="Y20" t="n">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="Z20" t="n">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.846</v>
+        <v>0.848</v>
       </c>
       <c r="AB20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AC20" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.545</v>
+        <v>0.519</v>
       </c>
       <c r="AE20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.444</v>
+        <v>0.455</v>
       </c>
       <c r="AH20" t="n">
         <v>1</v>
@@ -3435,48 +3435,48 @@
         <v>11</v>
       </c>
       <c r="AL20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.393</v>
+        <v>0.367</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>419:17</t>
+          <t>501:19</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>157.08</v>
+        <v>184.68</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.622</v>
+        <v>0.602</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.723</v>
+        <v>0.713</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.235</v>
+        <v>1.202</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.146</v>
+        <v>0.157</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.735</v>
+        <v>0.761</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.304</v>
+        <v>1.172</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.165</v>
+        <v>0.161</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.094</v>
+        <v>0.106</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.2</v>
+        <v>0.194</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.041</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="21">
@@ -3486,156 +3486,156 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C21" t="n">
-        <v>271</v>
+        <v>342</v>
       </c>
       <c r="D21" t="n">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="E21" t="n">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G21" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="H21" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="I21" t="n">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="J21" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="K21" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="L21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M21" t="n">
+        <v>34</v>
+      </c>
+      <c r="N21" t="n">
+        <v>12</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>64</v>
+      </c>
+      <c r="R21" t="n">
+        <v>91</v>
+      </c>
+      <c r="S21" t="n">
+        <v>158</v>
+      </c>
+      <c r="T21" t="n">
+        <v>341</v>
+      </c>
+      <c r="U21" t="n">
+        <v>53</v>
+      </c>
+      <c r="V21" t="n">
+        <v>34</v>
+      </c>
+      <c r="W21" t="n">
+        <v>41</v>
+      </c>
+      <c r="X21" t="n">
         <v>27</v>
       </c>
-      <c r="N21" t="n">
-        <v>11</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>58</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>58</v>
-      </c>
-      <c r="R21" t="n">
-        <v>80</v>
-      </c>
-      <c r="S21" t="n">
-        <v>128</v>
-      </c>
-      <c r="T21" t="n">
-        <v>257</v>
-      </c>
-      <c r="U21" t="n">
-        <v>38</v>
-      </c>
-      <c r="V21" t="n">
-        <v>29</v>
-      </c>
-      <c r="W21" t="n">
+      <c r="Y21" t="n">
+        <v>182</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>249</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF21" t="n">
         <v>27</v>
       </c>
-      <c r="X21" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>146</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>201</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>25</v>
-      </c>
       <c r="AG21" t="n">
-        <v>0.2</v>
+        <v>0.222</v>
       </c>
       <c r="AH21" t="n">
         <v>6</v>
       </c>
       <c r="AI21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.462</v>
+        <v>0.429</v>
       </c>
       <c r="AK21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL21" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.205</v>
+        <v>0.234</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>514:23</t>
+          <t>601:05</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>302.8</v>
+        <v>364.44</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.479</v>
+        <v>0.498</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.554</v>
+        <v>0.569</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.895</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.192</v>
+        <v>0.176</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.453</v>
+        <v>0.466</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.793</v>
+        <v>0.875</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.26</v>
+        <v>0.266</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.089</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.065</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -3785,16 +3785,16 @@
         <v>0.846</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.253</v>
+        <v>0.251</v>
       </c>
       <c r="AW22" t="n">
         <v>0.098</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.146</v>
+        <v>0.145</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="23">
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C23" t="n">
         <v>22</v>
@@ -3813,13 +3813,13 @@
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
@@ -3852,13 +3852,13 @@
         <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
       </c>
       <c r="T23" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="U23" t="n">
         <v>10</v>
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -3912,48 +3912,48 @@
         <v>2</v>
       </c>
       <c r="AL23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.2</v>
+        <v>0.182</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>81:36</t>
+          <t>84:42</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>36.08</v>
+        <v>38.08</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.404</v>
+        <v>0.375</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.378</v>
+        <v>0.354</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.61</v>
+        <v>0.578</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.194</v>
+        <v>0.184</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="AU23" t="n">
         <v>0.571</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.195</v>
+        <v>0.197</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.04</v>
+        <v>0.038</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="24">
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.277</v>
+        <v>0.275</v>
       </c>
       <c r="AW24" t="n">
         <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="25">
@@ -4421,7 +4421,7 @@
         <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.172</v>
+        <v>0.171</v>
       </c>
       <c r="AW26" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.143</v>
+        <v>0.142</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.173</v>
+        <v>0.172</v>
       </c>
       <c r="AX28" t="n">
         <v>0.08799999999999999</v>
@@ -4758,61 +4758,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C29" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D29" t="n">
+        <v>12</v>
+      </c>
+      <c r="E29" t="n">
+        <v>46</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>32</v>
+      </c>
+      <c r="H29" t="n">
+        <v>7</v>
+      </c>
+      <c r="I29" t="n">
         <v>9</v>
       </c>
-      <c r="E29" t="n">
-        <v>36</v>
-      </c>
-      <c r="F29" t="n">
+      <c r="J29" t="n">
+        <v>60</v>
+      </c>
+      <c r="K29" t="n">
+        <v>21</v>
+      </c>
+      <c r="L29" t="n">
         <v>5</v>
       </c>
-      <c r="G29" t="n">
-        <v>23</v>
-      </c>
-      <c r="H29" t="n">
-        <v>5</v>
-      </c>
-      <c r="I29" t="n">
-        <v>7</v>
-      </c>
-      <c r="J29" t="n">
-        <v>50</v>
-      </c>
-      <c r="K29" t="n">
-        <v>18</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
+        <v>6</v>
+      </c>
+      <c r="N29" t="n">
         <v>4</v>
       </c>
-      <c r="M29" t="n">
-        <v>4</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2</v>
-      </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="Q29" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="R29" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="S29" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="T29" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="U29" t="n">
         <v>5</v>
@@ -4827,87 +4827,87 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z29" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.5</v>
+        <v>0.478</v>
       </c>
       <c r="AB29" t="n">
         <v>4</v>
       </c>
       <c r="AC29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM29" t="n">
         <v>0.267</v>
       </c>
-      <c r="AE29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0.227</v>
-      </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>201:21</t>
+          <t>269:19</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>88.08</v>
+        <v>114.96</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.28</v>
+        <v>0.308</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.306</v>
+        <v>0.336</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.431</v>
+        <v>0.478</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.295</v>
+        <v>0.287</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.923</v>
+        <v>1.818</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.193</v>
+        <v>0.187</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.097</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.064</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="30">
@@ -5057,7 +5057,7 @@
         <v>0.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.24</v>
+        <v>0.238</v>
       </c>
       <c r="AW30" t="n">
         <v>0.033</v>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -5103,10 +5103,10 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -5118,19 +5118,19 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
         <v>0</v>
@@ -5231,157 +5231,157 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>2751</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>601</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1177</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>909</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>604</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>798</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="K32" t="n">
-        <v>44</v>
+        <v>757</v>
       </c>
       <c r="L32" t="n">
-        <v>53</v>
+        <v>375</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>22</v>
+        <v>497</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>466</v>
       </c>
       <c r="R32" t="n">
-        <v>9</v>
+        <v>763</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>785</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3015</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1005</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1379</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>0.729</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>0.321</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>0.345</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>6425:00</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>2934.12</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>0.515</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>0.169</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>1.147</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
@@ -5390,157 +5390,157 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>2373</v>
+        <v>2913</v>
       </c>
       <c r="D33" t="n">
-        <v>524</v>
+        <v>739</v>
       </c>
       <c r="E33" t="n">
-        <v>1031</v>
+        <v>1341</v>
       </c>
       <c r="F33" t="n">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="G33" t="n">
-        <v>787</v>
+        <v>809</v>
       </c>
       <c r="H33" t="n">
-        <v>515</v>
+        <v>589</v>
       </c>
       <c r="I33" t="n">
-        <v>681</v>
+        <v>781</v>
       </c>
       <c r="J33" t="n">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="K33" t="n">
-        <v>655</v>
+        <v>834</v>
       </c>
       <c r="L33" t="n">
-        <v>324</v>
+        <v>430</v>
       </c>
       <c r="M33" t="n">
-        <v>176</v>
+        <v>264</v>
       </c>
       <c r="N33" t="n">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>433</v>
+        <v>503</v>
       </c>
       <c r="Q33" t="n">
-        <v>411</v>
+        <v>467</v>
       </c>
       <c r="R33" t="n">
-        <v>666</v>
+        <v>794</v>
       </c>
       <c r="S33" t="n">
-        <v>678</v>
+        <v>755</v>
       </c>
       <c r="T33" t="n">
-        <v>2581</v>
+        <v>3274</v>
       </c>
       <c r="U33" t="n">
-        <v>315</v>
+        <v>381</v>
       </c>
       <c r="V33" t="n">
-        <v>331</v>
+        <v>422</v>
       </c>
       <c r="W33" t="n">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="X33" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="Y33" t="n">
-        <v>871</v>
+        <v>1115</v>
       </c>
       <c r="Z33" t="n">
-        <v>1200</v>
+        <v>1561</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.726</v>
+        <v>0.714</v>
       </c>
       <c r="AB33" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="AC33" t="n">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.338</v>
+        <v>0.382</v>
       </c>
       <c r="AE33" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AF33" t="n">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.312</v>
+        <v>0.376</v>
       </c>
       <c r="AH33" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="AI33" t="n">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.354</v>
+        <v>0.406</v>
       </c>
       <c r="AK33" t="n">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="AL33" t="n">
-        <v>589</v>
+        <v>671</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.34</v>
+        <v>0.337</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>5625:00</t>
+          <t>6425:00</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>2550.64</v>
+        <v>2996.64</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.511</v>
+        <v>0.54</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.584</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.93</v>
+        <v>0.972</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.17</v>
+        <v>0.168</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.283</v>
+        <v>0.274</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.15</v>
+        <v>1.012</v>
       </c>
       <c r="AV33" t="n">
         <v>0.2</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.061</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.127</v>
+        <v>0.138</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
@@ -5549,2672 +5549,2672 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>28</v>
-      </c>
-      <c r="C34" t="n">
-        <v>2550</v>
-      </c>
-      <c r="D34" t="n">
-        <v>650</v>
-      </c>
-      <c r="E34" t="n">
-        <v>1177</v>
-      </c>
-      <c r="F34" t="n">
-        <v>246</v>
-      </c>
-      <c r="G34" t="n">
-        <v>700</v>
-      </c>
-      <c r="H34" t="n">
-        <v>512</v>
-      </c>
-      <c r="I34" t="n">
-        <v>676</v>
-      </c>
-      <c r="J34" t="n">
-        <v>449</v>
-      </c>
-      <c r="K34" t="n">
-        <v>730</v>
-      </c>
-      <c r="L34" t="n">
-        <v>377</v>
-      </c>
-      <c r="M34" t="n">
-        <v>234</v>
-      </c>
-      <c r="N34" t="n">
-        <v>160</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>435</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>402</v>
-      </c>
-      <c r="R34" t="n">
-        <v>685</v>
-      </c>
-      <c r="S34" t="n">
-        <v>661</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2896</v>
-      </c>
-      <c r="U34" t="n">
-        <v>348</v>
-      </c>
-      <c r="V34" t="n">
-        <v>372</v>
-      </c>
-      <c r="W34" t="n">
-        <v>144</v>
-      </c>
-      <c r="X34" t="n">
-        <v>92</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>974</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1372</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>109</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>288</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>79</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>193</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>50</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>126</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0.397</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>196</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>574</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>5625:00</t>
-        </is>
-      </c>
-      <c r="AO34" t="n">
-        <v>2609.44</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0.543</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0.977</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>1.032</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr"/>
-      <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="inlineStr"/>
-      <c r="AP35" t="inlineStr"/>
-      <c r="AQ35" t="inlineStr"/>
-      <c r="AR35" t="inlineStr"/>
-      <c r="AS35" t="inlineStr"/>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AU35" t="inlineStr"/>
-      <c r="AV35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr"/>
-      <c r="AX35" t="inlineStr"/>
-      <c r="AY35" t="inlineStr"/>
+          <t>#0 K. AKOBUNDU (Per Game)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>32</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4.781</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.812</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.062</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.656</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="T35" t="n">
+        <v>213</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2.969</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.844</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AO35" t="n">
+        <v>3.512</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0.012</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#0 K. AKOBUNDU (Per Game)</t>
+          <t>#2 H. BENITEZ (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C36" t="n">
-        <v>5.107</v>
+        <v>10.5</v>
       </c>
       <c r="D36" t="n">
-        <v>1.964</v>
+        <v>3.5</v>
       </c>
       <c r="E36" t="n">
-        <v>2.25</v>
+        <v>7.643</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.786</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2.143</v>
       </c>
       <c r="H36" t="n">
-        <v>1.179</v>
+        <v>1.143</v>
       </c>
       <c r="I36" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4.786</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.214</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.071</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.071</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.357</v>
+      </c>
+      <c r="S36" t="n">
         <v>1.929</v>
       </c>
-      <c r="J36" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1.429</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1.714</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="R36" t="n">
-        <v>2.143</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1.25</v>
-      </c>
       <c r="T36" t="n">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="U36" t="n">
-        <v>0.571</v>
+        <v>1.929</v>
       </c>
       <c r="V36" t="n">
         <v>0.786</v>
       </c>
       <c r="W36" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.429</v>
       </c>
       <c r="X36" t="n">
-        <v>0.036</v>
+        <v>0.214</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.143</v>
+        <v>2.571</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.071</v>
+        <v>4.214</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.772</v>
+        <v>0.61</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.07099999999999999</v>
+        <v>2.571</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>0.389</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.071</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.036</v>
+        <v>2.429</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>0.441</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.714</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>3.741</v>
+        <v>12.549</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.873</v>
+        <v>0.478</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.824</v>
+        <v>0.501</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.365</v>
+        <v>0.837</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.172</v>
+        <v>0.165</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.524</v>
+        <v>0.117</v>
       </c>
       <c r="AU36" t="n">
-        <v>0.556</v>
+        <v>2.31</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.118</v>
+        <v>0.27</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.076</v>
+        <v>0.041</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.111</v>
+        <v>0.091</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.014</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#2 H. BENITEZ (Per Game)</t>
+          <t>#3 D. DUKE JR (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C37" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I37" t="n">
         <v>3.5</v>
       </c>
-      <c r="E37" t="n">
-        <v>7.643</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.786</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2.143</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1.143</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1.571</v>
-      </c>
       <c r="J37" t="n">
-        <v>4.786</v>
+        <v>1.875</v>
       </c>
       <c r="K37" t="n">
-        <v>1.714</v>
+        <v>1.125</v>
       </c>
       <c r="L37" t="n">
-        <v>0.786</v>
+        <v>1.25</v>
       </c>
       <c r="M37" t="n">
-        <v>1.214</v>
+        <v>0.375</v>
       </c>
       <c r="N37" t="n">
-        <v>0.357</v>
+        <v>0.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.071</v>
+        <v>1.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.071</v>
+        <v>1.75</v>
       </c>
       <c r="R37" t="n">
-        <v>2.357</v>
+        <v>2.25</v>
       </c>
       <c r="S37" t="n">
-        <v>1.929</v>
+        <v>2.5</v>
       </c>
       <c r="T37" t="n">
-        <v>153</v>
+        <v>46</v>
       </c>
       <c r="U37" t="n">
-        <v>1.929</v>
+        <v>0.25</v>
       </c>
       <c r="V37" t="n">
-        <v>0.786</v>
+        <v>0.625</v>
       </c>
       <c r="W37" t="n">
-        <v>0.429</v>
+        <v>1.5</v>
       </c>
       <c r="X37" t="n">
-        <v>0.214</v>
+        <v>1.125</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.571</v>
+        <v>3.625</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.214</v>
+        <v>5</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.61</v>
+        <v>0.725</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.571</v>
+        <v>0.625</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.389</v>
+        <v>0.4</v>
       </c>
       <c r="AE37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AO37" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="AU37" t="n">
         <v>1.071</v>
       </c>
-      <c r="AF37" t="n">
-        <v>2.429</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.714</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>20:22</t>
-        </is>
-      </c>
-      <c r="AO37" t="n">
-        <v>12.549</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0.478</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0.501</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>0.837</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>2.31</v>
-      </c>
       <c r="AV37" t="n">
-        <v>0.272</v>
+        <v>0.236</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.041</v>
+        <v>0.077</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.092</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.199</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#3 D. DUKE JR (Per Game)</t>
+          <t>#4 M. GASPÀ (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>0.625</v>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>0.875</v>
       </c>
       <c r="F38" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="M38" t="n">
         <v>0.25</v>
       </c>
-      <c r="G38" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
       <c r="N38" t="n">
-        <v>0.5</v>
+        <v>0.125</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.75</v>
+        <v>0.188</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.75</v>
+        <v>0.188</v>
       </c>
       <c r="R38" t="n">
-        <v>3.25</v>
+        <v>1.312</v>
       </c>
       <c r="S38" t="n">
-        <v>3.25</v>
+        <v>0.875</v>
       </c>
       <c r="T38" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="U38" t="n">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="W38" t="n">
-        <v>2.5</v>
+        <v>0.312</v>
       </c>
       <c r="X38" t="n">
-        <v>2</v>
+        <v>0.125</v>
       </c>
       <c r="Y38" t="n">
-        <v>5.25</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.75</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.778</v>
+        <v>0.733</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.25</v>
+        <v>0.312</v>
       </c>
       <c r="AC38" t="n">
-        <v>1</v>
+        <v>0.375</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.25</v>
+        <v>0.833</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.75</v>
+        <v>0.062</v>
       </c>
       <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AM38" t="n">
         <v>0.333</v>
       </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0.125</v>
-      </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>11.23</v>
+        <v>1.72</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.317</v>
+        <v>0.619</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.448</v>
+        <v>0.653</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.757</v>
+        <v>1.163</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.156</v>
+        <v>0.109</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.5</v>
+        <v>0.286</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.429</v>
+        <v>3.333</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.241</v>
+        <v>0.117</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.065</v>
+        <v>0.052</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.079</v>
+        <v>0.063</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.029</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#4 M. GASPÀ (Per Game)</t>
+          <t>#6 F. BASSAS (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C39" t="n">
+        <v>10.455</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.409</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.045</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5.909</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I39" t="n">
         <v>2</v>
       </c>
-      <c r="D39" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.5</v>
-      </c>
       <c r="J39" t="n">
-        <v>0.625</v>
+        <v>6.227</v>
       </c>
       <c r="K39" t="n">
-        <v>0.375</v>
+        <v>1.182</v>
       </c>
       <c r="L39" t="n">
-        <v>0.312</v>
+        <v>0.409</v>
       </c>
       <c r="M39" t="n">
-        <v>0.25</v>
+        <v>1.045</v>
       </c>
       <c r="N39" t="n">
-        <v>0.125</v>
+        <v>0.227</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.188</v>
+        <v>2.636</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.188</v>
+        <v>2.636</v>
       </c>
       <c r="R39" t="n">
-        <v>1.312</v>
+        <v>2.5</v>
       </c>
       <c r="S39" t="n">
-        <v>0.875</v>
+        <v>2.545</v>
       </c>
       <c r="T39" t="n">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="U39" t="n">
-        <v>0.375</v>
+        <v>1.364</v>
       </c>
       <c r="V39" t="n">
-        <v>0.312</v>
+        <v>1.409</v>
       </c>
       <c r="W39" t="n">
-        <v>0.312</v>
+        <v>0.864</v>
       </c>
       <c r="X39" t="n">
-        <v>0.125</v>
+        <v>0.409</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.6879999999999999</v>
+        <v>2.136</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.9379999999999999</v>
+        <v>3.455</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.733</v>
+        <v>0.618</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.312</v>
+        <v>0.636</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.375</v>
+        <v>1.545</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.833</v>
+        <v>0.412</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.062</v>
+        <v>0.455</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>0.364</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.062</v>
+        <v>1</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>0.364</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.125</v>
+        <v>1.682</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.375</v>
+        <v>4.909</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.333</v>
+        <v>0.343</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>1.72</v>
+        <v>12.88</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.619</v>
+        <v>0.478</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.653</v>
+        <v>0.51</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.163</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.109</v>
+        <v>0.205</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.286</v>
+        <v>0.16</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.333</v>
+        <v>2.362</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.118</v>
+        <v>0.263</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.052</v>
+        <v>0.02</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.064</v>
+        <v>0.06</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.023</v>
+        <v>0.247</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#6 F. BASSAS (Per Game)</t>
+          <t>#8 A. REYES (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C40" t="n">
-        <v>9.555999999999999</v>
+        <v>13.581</v>
       </c>
       <c r="D40" t="n">
-        <v>1.333</v>
+        <v>1.452</v>
       </c>
       <c r="E40" t="n">
-        <v>3.278</v>
+        <v>2.968</v>
       </c>
       <c r="F40" t="n">
-        <v>1.833</v>
+        <v>2.71</v>
       </c>
       <c r="G40" t="n">
-        <v>5.722</v>
+        <v>6.613</v>
       </c>
       <c r="H40" t="n">
-        <v>1.389</v>
+        <v>2.548</v>
       </c>
       <c r="I40" t="n">
-        <v>1.833</v>
+        <v>3.226</v>
       </c>
       <c r="J40" t="n">
-        <v>6.5</v>
+        <v>0.774</v>
       </c>
       <c r="K40" t="n">
-        <v>1.278</v>
+        <v>4.194</v>
       </c>
       <c r="L40" t="n">
-        <v>0.389</v>
+        <v>0.903</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0.742</v>
       </c>
       <c r="N40" t="n">
-        <v>0.278</v>
+        <v>0.194</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.722</v>
+        <v>1.032</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.722</v>
+        <v>1.032</v>
       </c>
       <c r="R40" t="n">
-        <v>2.5</v>
+        <v>2.032</v>
       </c>
       <c r="S40" t="n">
-        <v>2.556</v>
+        <v>2.581</v>
       </c>
       <c r="T40" t="n">
-        <v>181</v>
+        <v>428</v>
       </c>
       <c r="U40" t="n">
-        <v>0.944</v>
+        <v>2.129</v>
       </c>
       <c r="V40" t="n">
-        <v>1.111</v>
+        <v>1.677</v>
       </c>
       <c r="W40" t="n">
-        <v>0.778</v>
+        <v>1.129</v>
       </c>
       <c r="X40" t="n">
-        <v>0.389</v>
+        <v>0.645</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.111</v>
+        <v>3.419</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.444</v>
+        <v>4.419</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.613</v>
+        <v>0.774</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.444</v>
+        <v>0.258</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.167</v>
+        <v>0.71</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.381</v>
+        <v>0.364</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.167</v>
+        <v>0.323</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.5</v>
+        <v>1.065</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.333</v>
+        <v>0.303</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.278</v>
+        <v>0.581</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.833</v>
+        <v>1.581</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.333</v>
+        <v>0.367</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.556</v>
+        <v>2.129</v>
       </c>
       <c r="AL40" t="n">
-        <v>4.889</v>
+        <v>5.032</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.318</v>
+        <v>0.423</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>25:11</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>12.529</v>
+        <v>12.032</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.454</v>
+        <v>0.576</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.487</v>
+        <v>0.617</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.763</v>
+        <v>1.129</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.217</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.154</v>
+        <v>0.266</v>
       </c>
       <c r="AU40" t="n">
-        <v>2.388</v>
+        <v>0.75</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.258</v>
+        <v>0.209</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.019</v>
+        <v>0.038</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.065</v>
+        <v>0.18</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.258</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#8 A. REYES (Per Game)</t>
+          <t>#11 A. UBAL (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C41" t="n">
-        <v>13.556</v>
+        <v>9.586</v>
       </c>
       <c r="D41" t="n">
-        <v>1.407</v>
+        <v>2.172</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>4.379</v>
       </c>
       <c r="F41" t="n">
-        <v>2.704</v>
+        <v>0.759</v>
       </c>
       <c r="G41" t="n">
-        <v>6.444</v>
+        <v>2.517</v>
       </c>
       <c r="H41" t="n">
-        <v>2.63</v>
+        <v>2.966</v>
       </c>
       <c r="I41" t="n">
-        <v>3.37</v>
+        <v>3.517</v>
       </c>
       <c r="J41" t="n">
-        <v>0.704</v>
+        <v>1.103</v>
       </c>
       <c r="K41" t="n">
-        <v>4.148</v>
+        <v>2.724</v>
       </c>
       <c r="L41" t="n">
-        <v>0.926</v>
+        <v>0.724</v>
       </c>
       <c r="M41" t="n">
-        <v>0.593</v>
+        <v>0.759</v>
       </c>
       <c r="N41" t="n">
-        <v>0.222</v>
+        <v>0.655</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.074</v>
+        <v>1.759</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.074</v>
+        <v>1.759</v>
       </c>
       <c r="R41" t="n">
-        <v>2</v>
+        <v>1.483</v>
       </c>
       <c r="S41" t="n">
-        <v>2.556</v>
+        <v>3.655</v>
       </c>
       <c r="T41" t="n">
-        <v>366</v>
+        <v>332</v>
       </c>
       <c r="U41" t="n">
-        <v>2.111</v>
+        <v>1.414</v>
       </c>
       <c r="V41" t="n">
-        <v>1.667</v>
+        <v>1.069</v>
       </c>
       <c r="W41" t="n">
-        <v>1.222</v>
+        <v>1.241</v>
       </c>
       <c r="X41" t="n">
-        <v>0.667</v>
+        <v>0.793</v>
       </c>
       <c r="Y41" t="n">
-        <v>3.519</v>
+        <v>4.414</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.63</v>
+        <v>5.724</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.76</v>
+        <v>0.771</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.222</v>
+        <v>0.448</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.704</v>
+        <v>1.517</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.316</v>
+        <v>0.295</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.296</v>
+        <v>0.276</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.037</v>
+        <v>0.655</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.286</v>
+        <v>0.421</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.481</v>
+        <v>0.276</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.296</v>
+        <v>0.655</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.371</v>
+        <v>0.421</v>
       </c>
       <c r="AK41" t="n">
-        <v>2.222</v>
+        <v>0.483</v>
       </c>
       <c r="AL41" t="n">
-        <v>5.148</v>
+        <v>1.862</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.432</v>
+        <v>0.259</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>25:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>12.001</v>
+        <v>10.203</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.578</v>
+        <v>0.48</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.62</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.129</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.089</v>
+        <v>0.172</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.278</v>
+        <v>0.43</v>
       </c>
       <c r="AU41" t="n">
-        <v>0.655</v>
+        <v>0.627</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.209</v>
+        <v>0.229</v>
       </c>
       <c r="AW41" t="n">
         <v>0.039</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.178</v>
+        <v>0.151</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.029</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#11 A. UBAL (Per Game)</t>
+          <t>#12 M. STEINBERGS (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C42" t="n">
-        <v>9.119999999999999</v>
+        <v>6.531</v>
       </c>
       <c r="D42" t="n">
-        <v>2.08</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>4.4</v>
+        <v>1.469</v>
       </c>
       <c r="F42" t="n">
-        <v>0.72</v>
+        <v>1.5</v>
       </c>
       <c r="G42" t="n">
-        <v>2.52</v>
+        <v>4.188</v>
       </c>
       <c r="H42" t="n">
-        <v>2.8</v>
+        <v>0.656</v>
       </c>
       <c r="I42" t="n">
-        <v>3.28</v>
+        <v>0.844</v>
       </c>
       <c r="J42" t="n">
-        <v>1.24</v>
+        <v>0.781</v>
       </c>
       <c r="K42" t="n">
-        <v>2.72</v>
+        <v>1.531</v>
       </c>
       <c r="L42" t="n">
-        <v>0.64</v>
+        <v>0.906</v>
       </c>
       <c r="M42" t="n">
-        <v>0.76</v>
+        <v>0.25</v>
       </c>
       <c r="N42" t="n">
-        <v>0.68</v>
+        <v>0.344</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.84</v>
+        <v>0.531</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.84</v>
+        <v>0.531</v>
       </c>
       <c r="R42" t="n">
-        <v>1.52</v>
+        <v>2.062</v>
       </c>
       <c r="S42" t="n">
-        <v>3.6</v>
+        <v>0.875</v>
       </c>
       <c r="T42" t="n">
-        <v>270</v>
+        <v>159</v>
       </c>
       <c r="U42" t="n">
-        <v>1.52</v>
+        <v>0.344</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>1.188</v>
       </c>
       <c r="W42" t="n">
-        <v>1.2</v>
+        <v>0.406</v>
       </c>
       <c r="X42" t="n">
-        <v>0.72</v>
+        <v>0.188</v>
       </c>
       <c r="Y42" t="n">
-        <v>4.16</v>
+        <v>1.062</v>
       </c>
       <c r="Z42" t="n">
-        <v>5.52</v>
+        <v>1.531</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.754</v>
+        <v>0.694</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.44</v>
+        <v>0.156</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.52</v>
+        <v>0.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.289</v>
+        <v>0.312</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.28</v>
+        <v>0.125</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.64</v>
+        <v>0.281</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.24</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.6</v>
+        <v>1.625</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.4</v>
+        <v>0.346</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.48</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.92</v>
+        <v>2.562</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.25</v>
+        <v>0.366</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>10.203</v>
+        <v>6.559</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.457</v>
+        <v>0.519</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.545</v>
+        <v>0.542</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.894</v>
+        <v>0.996</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.18</v>
+        <v>0.081</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.405</v>
+        <v>0.116</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.674</v>
+        <v>1.471</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.229</v>
+        <v>0.141</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.035</v>
+        <v>0.047</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.151</v>
+        <v>0.081</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.049</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#12 M. STEINBERGS (Per Game)</t>
+          <t>#18 G. KNUDSEN (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>28</v>
       </c>
       <c r="C43" t="n">
-        <v>6.75</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
+        <v>1.107</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.679</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="M43" t="n">
         <v>0.643</v>
       </c>
-      <c r="E43" t="n">
-        <v>1.286</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1.571</v>
-      </c>
-      <c r="G43" t="n">
-        <v>4.393</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.964</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.893</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1.536</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.964</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.25</v>
-      </c>
       <c r="N43" t="n">
-        <v>0.357</v>
+        <v>0.643</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.5</v>
+        <v>0.607</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.5</v>
+        <v>0.607</v>
       </c>
       <c r="R43" t="n">
-        <v>1.964</v>
+        <v>1.321</v>
       </c>
       <c r="S43" t="n">
-        <v>0.929</v>
+        <v>0.464</v>
       </c>
       <c r="T43" t="n">
-        <v>155</v>
+        <v>106</v>
       </c>
       <c r="U43" t="n">
-        <v>0.393</v>
+        <v>0.464</v>
       </c>
       <c r="V43" t="n">
-        <v>1.25</v>
+        <v>0.714</v>
       </c>
       <c r="W43" t="n">
-        <v>0.357</v>
+        <v>0.286</v>
       </c>
       <c r="X43" t="n">
         <v>0.179</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.107</v>
+        <v>1.214</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.607</v>
+        <v>1.857</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.654</v>
       </c>
       <c r="AB43" t="n">
         <v>0.179</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.393</v>
+        <v>0.571</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.455</v>
+        <v>0.312</v>
       </c>
       <c r="AE43" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AF43" t="n">
         <v>0.107</v>
       </c>
-      <c r="AF43" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AG43" t="n">
-        <v>0.429</v>
+        <v>0.667</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.643</v>
+        <v>0.036</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.786</v>
+        <v>0.464</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.36</v>
+        <v>0.077</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.929</v>
+        <v>0.107</v>
       </c>
       <c r="AL43" t="n">
-        <v>2.607</v>
+        <v>0.321</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.356</v>
+        <v>0.333</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>6.603</v>
+        <v>3.589</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.528</v>
+        <v>0.487</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.553</v>
+        <v>0.503</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.022</v>
+        <v>0.836</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.076</v>
+        <v>0.169</v>
       </c>
       <c r="AT43" t="n">
         <v>0.132</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.786</v>
+        <v>0.647</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.14</v>
+        <v>0.132</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.049</v>
+        <v>0.054</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.08</v>
+        <v>0.153</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.034</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#18 G. KNUDSEN (Per Game)</t>
+          <t>#19 L. OLINDE (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C44" t="n">
-        <v>2.667</v>
+        <v>7.87</v>
       </c>
       <c r="D44" t="n">
-        <v>1.083</v>
+        <v>1.565</v>
       </c>
       <c r="E44" t="n">
-        <v>1.792</v>
+        <v>2.957</v>
       </c>
       <c r="F44" t="n">
-        <v>0.083</v>
+        <v>1.13</v>
       </c>
       <c r="G44" t="n">
-        <v>0.708</v>
+        <v>2.739</v>
       </c>
       <c r="H44" t="n">
-        <v>0.25</v>
+        <v>1.348</v>
       </c>
       <c r="I44" t="n">
-        <v>0.458</v>
+        <v>2.043</v>
       </c>
       <c r="J44" t="n">
-        <v>0.25</v>
+        <v>0.696</v>
       </c>
       <c r="K44" t="n">
-        <v>1.167</v>
+        <v>2.522</v>
       </c>
       <c r="L44" t="n">
-        <v>0.583</v>
+        <v>1.739</v>
       </c>
       <c r="M44" t="n">
-        <v>0.583</v>
+        <v>0.783</v>
       </c>
       <c r="N44" t="n">
-        <v>0.458</v>
+        <v>0.696</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.5</v>
+        <v>1.217</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.5</v>
+        <v>1.217</v>
       </c>
       <c r="R44" t="n">
-        <v>1.208</v>
+        <v>2</v>
       </c>
       <c r="S44" t="n">
-        <v>0.417</v>
+        <v>2.783</v>
       </c>
       <c r="T44" t="n">
-        <v>69</v>
+        <v>234</v>
       </c>
       <c r="U44" t="n">
-        <v>0.5</v>
+        <v>1.217</v>
       </c>
       <c r="V44" t="n">
-        <v>0.667</v>
+        <v>1.174</v>
       </c>
       <c r="W44" t="n">
-        <v>0.333</v>
+        <v>0.87</v>
       </c>
       <c r="X44" t="n">
-        <v>0.208</v>
+        <v>0.522</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.167</v>
+        <v>2.696</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.708</v>
+        <v>3.87</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.697</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.083</v>
+        <v>0.174</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.458</v>
+        <v>0.826</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.182</v>
+        <v>0.211</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.083</v>
+        <v>0.043</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.083</v>
+        <v>0.304</v>
       </c>
       <c r="AG44" t="n">
-        <v>1</v>
+        <v>0.143</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>0.522</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.375</v>
+        <v>0.957</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.083</v>
+        <v>0.609</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.333</v>
+        <v>1.783</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.25</v>
+        <v>0.341</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>3.202</v>
+        <v>7.812</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.483</v>
+        <v>0.573</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.494</v>
+        <v>0.597</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.833</v>
+        <v>1.007</v>
       </c>
       <c r="AS44" t="n">
         <v>0.156</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.1</v>
+        <v>0.237</v>
       </c>
       <c r="AU44" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.135</v>
+        <v>0.159</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.06</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.122</v>
+        <v>0.127</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#19 L. OLINDE (Per Game)</t>
+          <t>#22 P. PAULICAP (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C45" t="n">
-        <v>7.81</v>
+        <v>1.462</v>
       </c>
       <c r="D45" t="n">
-        <v>1.476</v>
+        <v>0.462</v>
       </c>
       <c r="E45" t="n">
-        <v>2.81</v>
+        <v>0.923</v>
       </c>
       <c r="F45" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>2.905</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.286</v>
+        <v>0.538</v>
       </c>
       <c r="I45" t="n">
-        <v>1.905</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>2.476</v>
+        <v>0.385</v>
       </c>
       <c r="L45" t="n">
-        <v>1.81</v>
+        <v>0.385</v>
       </c>
       <c r="M45" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0.667</v>
+        <v>0.538</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.333</v>
+        <v>0.462</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.333</v>
+        <v>0.462</v>
       </c>
       <c r="R45" t="n">
-        <v>2.143</v>
+        <v>0.923</v>
       </c>
       <c r="S45" t="n">
-        <v>2.857</v>
+        <v>0.538</v>
       </c>
       <c r="T45" t="n">
-        <v>211</v>
+        <v>13</v>
       </c>
       <c r="U45" t="n">
-        <v>1.19</v>
+        <v>0.077</v>
       </c>
       <c r="V45" t="n">
-        <v>1.286</v>
+        <v>0.615</v>
       </c>
       <c r="W45" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0.524</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.524</v>
+        <v>0.923</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.619</v>
+        <v>1.462</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.697</v>
+        <v>0.632</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.19</v>
+        <v>0.077</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.462</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.235</v>
+        <v>0.167</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.048</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.545</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.619</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.857</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>22:13</t>
+          <t>04:24</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>7.886</v>
+        <v>1.825</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.596</v>
+        <v>0.536</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.99</v>
+        <v>0.801</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.169</v>
+        <v>0.253</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.225</v>
+        <v>0.583</v>
       </c>
       <c r="AU45" t="n">
-        <v>0.536</v>
+        <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.157</v>
+        <v>0.182</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.121</v>
+        <v>0.095</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#22 P. PAULICAP (Per Game)</t>
+          <t>#24 E. BROOKS (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C46" t="n">
-        <v>1.545</v>
+        <v>9</v>
       </c>
       <c r="D46" t="n">
-        <v>0.455</v>
+        <v>2.067</v>
       </c>
       <c r="E46" t="n">
-        <v>0.909</v>
+        <v>4.133</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2.733</v>
       </c>
       <c r="H46" t="n">
-        <v>0.636</v>
+        <v>2.067</v>
       </c>
       <c r="I46" t="n">
-        <v>1.182</v>
+        <v>2.533</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>2.933</v>
       </c>
       <c r="K46" t="n">
-        <v>0.455</v>
+        <v>1.933</v>
       </c>
       <c r="L46" t="n">
-        <v>0.364</v>
+        <v>0.733</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1.133</v>
       </c>
       <c r="N46" t="n">
-        <v>0.636</v>
+        <v>0.2</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.545</v>
+        <v>1.667</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.545</v>
+        <v>1.667</v>
       </c>
       <c r="R46" t="n">
-        <v>0.909</v>
+        <v>1.933</v>
       </c>
       <c r="S46" t="n">
-        <v>0.636</v>
+        <v>2.333</v>
       </c>
       <c r="T46" t="n">
-        <v>13</v>
+        <v>155</v>
       </c>
       <c r="U46" t="n">
-        <v>0.091</v>
+        <v>1.467</v>
       </c>
       <c r="V46" t="n">
-        <v>0.727</v>
+        <v>1.067</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>0.467</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.091</v>
+        <v>3.133</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.727</v>
+        <v>4.133</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.632</v>
+        <v>0.758</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.364</v>
+        <v>1.667</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>0.267</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>0.867</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>2.133</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>1.975</v>
+        <v>9.648</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.5</v>
+        <v>0.505</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.541</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AR46" t="n">
-        <v>0.783</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.276</v>
+        <v>0.173</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.7</v>
+        <v>0.301</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.177</v>
+        <v>0.208</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.079</v>
+        <v>0.038</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.101</v>
+        <v>0.103</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>#24 E. BROOKS (Per Game)</t>
+          <t>#29 P. ORIOLA (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C47" t="n">
-        <v>9.071</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>2.143</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>4.286</v>
+        <v>3.16</v>
       </c>
       <c r="F47" t="n">
-        <v>0.857</v>
+        <v>0.48</v>
       </c>
       <c r="G47" t="n">
-        <v>2.714</v>
+        <v>1.36</v>
       </c>
       <c r="H47" t="n">
-        <v>2.214</v>
+        <v>3.44</v>
       </c>
       <c r="I47" t="n">
-        <v>2.714</v>
+        <v>3.88</v>
       </c>
       <c r="J47" t="n">
-        <v>2.857</v>
+        <v>1.36</v>
       </c>
       <c r="K47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L47" t="n">
         <v>2</v>
       </c>
-      <c r="L47" t="n">
-        <v>0.714</v>
-      </c>
       <c r="M47" t="n">
-        <v>1.071</v>
+        <v>0.16</v>
       </c>
       <c r="N47" t="n">
-        <v>0.214</v>
+        <v>0.4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.643</v>
+        <v>1.16</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.643</v>
+        <v>1.16</v>
       </c>
       <c r="R47" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="S47" t="n">
-        <v>2.357</v>
+        <v>3.16</v>
       </c>
       <c r="T47" t="n">
-        <v>142</v>
+        <v>328</v>
       </c>
       <c r="U47" t="n">
-        <v>1.357</v>
+        <v>1</v>
       </c>
       <c r="V47" t="n">
-        <v>1.143</v>
+        <v>1.64</v>
       </c>
       <c r="W47" t="n">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="X47" t="n">
-        <v>0.429</v>
+        <v>0.72</v>
       </c>
       <c r="Y47" t="n">
-        <v>3.286</v>
+        <v>4.68</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.357</v>
+        <v>5.52</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.754</v>
+        <v>0.848</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.786</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.714</v>
+        <v>1.08</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.458</v>
+        <v>0.519</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.286</v>
+        <v>0.2</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.929</v>
+        <v>0.44</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.308</v>
+        <v>0.455</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.143</v>
+        <v>0.04</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.5</v>
+        <v>0.16</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.714</v>
+        <v>0.44</v>
       </c>
       <c r="AL47" t="n">
-        <v>2.214</v>
+        <v>1.2</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.323</v>
+        <v>0.367</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>9.837</v>
+        <v>7.387</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.49</v>
+        <v>0.602</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.554</v>
+        <v>0.713</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.922</v>
+        <v>1.202</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.167</v>
+        <v>0.157</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.316</v>
+        <v>0.761</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.739</v>
+        <v>1.172</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.213</v>
+        <v>0.161</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.037</v>
+        <v>0.106</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.107</v>
+        <v>0.194</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.113</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>#29 P. ORIOLA (Per Game)</t>
+          <t>#32 R. OBASOHAN (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C48" t="n">
-        <v>9.238</v>
+        <v>12.214</v>
       </c>
       <c r="D48" t="n">
-        <v>2.048</v>
+        <v>3.25</v>
       </c>
       <c r="E48" t="n">
-        <v>3.143</v>
+        <v>6.179</v>
       </c>
       <c r="F48" t="n">
-        <v>0.571</v>
+        <v>0.607</v>
       </c>
       <c r="G48" t="n">
-        <v>1.524</v>
+        <v>2.179</v>
       </c>
       <c r="H48" t="n">
-        <v>3.429</v>
+        <v>3.893</v>
       </c>
       <c r="I48" t="n">
-        <v>3.905</v>
+        <v>5.393</v>
       </c>
       <c r="J48" t="n">
-        <v>1.429</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
-        <v>3.667</v>
+        <v>1.75</v>
       </c>
       <c r="L48" t="n">
-        <v>1.762</v>
+        <v>0.464</v>
       </c>
       <c r="M48" t="n">
-        <v>0.19</v>
+        <v>1.214</v>
       </c>
       <c r="N48" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.095</v>
+        <v>2.286</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.095</v>
+        <v>2.286</v>
       </c>
       <c r="R48" t="n">
-        <v>2.667</v>
+        <v>3.25</v>
       </c>
       <c r="S48" t="n">
-        <v>3.238</v>
+        <v>5.643</v>
       </c>
       <c r="T48" t="n">
-        <v>285</v>
+        <v>341</v>
       </c>
       <c r="U48" t="n">
-        <v>0.857</v>
+        <v>1.893</v>
       </c>
       <c r="V48" t="n">
-        <v>1.524</v>
+        <v>1.214</v>
       </c>
       <c r="W48" t="n">
-        <v>0.952</v>
+        <v>1.464</v>
       </c>
       <c r="X48" t="n">
-        <v>0.762</v>
+        <v>0.964</v>
       </c>
       <c r="Y48" t="n">
-        <v>4.714</v>
+        <v>6.5</v>
       </c>
       <c r="Z48" t="n">
-        <v>5.571</v>
+        <v>8.893000000000001</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.846</v>
+        <v>0.731</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.571</v>
+        <v>0.429</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.048</v>
+        <v>1.714</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.545</v>
+        <v>0.25</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.19</v>
+        <v>0.214</v>
       </c>
       <c r="AF48" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ48" t="n">
         <v>0.429</v>
       </c>
-      <c r="AG48" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AK48" t="n">
-        <v>0.524</v>
+        <v>0.393</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.333</v>
+        <v>1.679</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.393</v>
+        <v>0.234</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>7.48</v>
+        <v>13.016</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.622</v>
+        <v>0.498</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.723</v>
+        <v>0.569</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.235</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.146</v>
+        <v>0.176</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.735</v>
+        <v>0.466</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.304</v>
+        <v>0.875</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.165</v>
+        <v>0.266</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.094</v>
+        <v>0.023</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.2</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.056</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>#32 R. OBASOHAN (Per Game)</t>
+          <t>#33 G. GOLDEN (Per Game)</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C49" t="n">
-        <v>11.292</v>
+        <v>7.133</v>
       </c>
       <c r="D49" t="n">
-        <v>2.958</v>
+        <v>3.133</v>
       </c>
       <c r="E49" t="n">
-        <v>5.833</v>
+        <v>6.867</v>
       </c>
       <c r="F49" t="n">
-        <v>0.583</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>2.167</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>3.625</v>
+        <v>0.867</v>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>1.267</v>
       </c>
       <c r="J49" t="n">
-        <v>1.917</v>
+        <v>1.467</v>
       </c>
       <c r="K49" t="n">
-        <v>1.75</v>
+        <v>2.133</v>
       </c>
       <c r="L49" t="n">
-        <v>0.417</v>
+        <v>1.467</v>
       </c>
       <c r="M49" t="n">
-        <v>1.125</v>
+        <v>0.2</v>
       </c>
       <c r="N49" t="n">
-        <v>0.458</v>
+        <v>0.667</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.417</v>
+        <v>1.733</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.417</v>
+        <v>1.733</v>
       </c>
       <c r="R49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T49" t="n">
+        <v>99</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.467</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>2.467</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>3.533</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="AC49" t="n">
         <v>3.333</v>
       </c>
-      <c r="S49" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="T49" t="n">
-        <v>257</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.583</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>6.083</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>8.375</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.417</v>
-      </c>
       <c r="AD49" t="n">
-        <v>0.206</v>
+        <v>0.34</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.208</v>
+        <v>0.4</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.042</v>
+        <v>1.267</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.2</v>
+        <v>0.316</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.542</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.625</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.205</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>21:25</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>12.617</v>
+        <v>9.157</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.479</v>
+        <v>0.456</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.554</v>
+        <v>0.48</v>
       </c>
       <c r="AR49" t="n">
-        <v>0.895</v>
+        <v>0.779</v>
       </c>
       <c r="AS49" t="n">
-        <v>0.192</v>
+        <v>0.189</v>
       </c>
       <c r="AT49" t="n">
-        <v>0.453</v>
+        <v>0.126</v>
       </c>
       <c r="AU49" t="n">
-        <v>0.793</v>
+        <v>0.846</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.26</v>
+        <v>0.251</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.021</v>
+        <v>0.098</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.089</v>
+        <v>0.145</v>
       </c>
       <c r="AY49" t="n">
-        <v>0.077</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>#33 G. GOLDEN (Per Game)</t>
+          <t>#42 G. FERNÁNDEZ (Per Game)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C50" t="n">
-        <v>7.133</v>
+        <v>1.571</v>
       </c>
       <c r="D50" t="n">
-        <v>3.133</v>
+        <v>0.214</v>
       </c>
       <c r="E50" t="n">
-        <v>6.867</v>
+        <v>0.714</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>0.357</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1.286</v>
       </c>
       <c r="H50" t="n">
-        <v>0.867</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>1.267</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
-        <v>1.467</v>
+        <v>0.286</v>
       </c>
       <c r="K50" t="n">
-        <v>2.133</v>
+        <v>0.214</v>
       </c>
       <c r="L50" t="n">
-        <v>1.467</v>
+        <v>0.214</v>
       </c>
       <c r="M50" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="N50" t="n">
-        <v>0.667</v>
+        <v>0.143</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.733</v>
+        <v>0.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.733</v>
+        <v>0.5</v>
       </c>
       <c r="R50" t="n">
-        <v>1.8</v>
+        <v>0.857</v>
       </c>
       <c r="S50" t="n">
-        <v>1.2</v>
+        <v>0.357</v>
       </c>
       <c r="T50" t="n">
-        <v>99</v>
+        <v>-4</v>
       </c>
       <c r="U50" t="n">
-        <v>0.333</v>
+        <v>0.714</v>
       </c>
       <c r="V50" t="n">
-        <v>1.467</v>
+        <v>0.214</v>
       </c>
       <c r="W50" t="n">
-        <v>0.267</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0.133</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.467</v>
+        <v>0.286</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.533</v>
+        <v>0.786</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.698</v>
+        <v>0.364</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.133</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.333</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.267</v>
+        <v>0.429</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.316</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>0.786</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>9.157</v>
+        <v>2.72</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.456</v>
+        <v>0.375</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.48</v>
+        <v>0.354</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.779</v>
+        <v>0.578</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.189</v>
+        <v>0.184</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.126</v>
+        <v>0.036</v>
       </c>
       <c r="AU50" t="n">
-        <v>0.846</v>
+        <v>0.571</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.253</v>
+        <v>0.197</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.098</v>
+        <v>0.038</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.146</v>
+        <v>0.038</v>
       </c>
       <c r="AY50" t="n">
-        <v>0.058</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>#42 G. FERNÁNDEZ (Per Game)</t>
+          <t>#43 L. SÁNCHEZ (Per Game)</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
         <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>0.273</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>0.8179999999999999</v>
+        <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>0.455</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>1.545</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>0.091</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0.636</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.364</v>
+        <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>0.273</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.182</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0.182</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>0.636</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.636</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
+        <v>3</v>
+      </c>
+      <c r="S51" t="n">
         <v>1</v>
       </c>
-      <c r="S51" t="n">
-        <v>0.455</v>
-      </c>
       <c r="T51" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>0.909</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
         <v>0</v>
@@ -8223,112 +8223,112 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.364</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
         <v>1</v>
       </c>
-      <c r="AA51" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.455</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.636</v>
+        <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>0.182</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
-        <v>0.909</v>
+        <v>1</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="AO51" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="AP51" t="n">
-        <v>0.404</v>
+        <v>0.25</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.378</v>
+        <v>0.25</v>
       </c>
       <c r="AR51" t="n">
-        <v>0.61</v>
+        <v>0.5</v>
       </c>
       <c r="AS51" t="n">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="AT51" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="AU51" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.195</v>
+        <v>0.275</v>
       </c>
       <c r="AW51" t="n">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="AX51" t="n">
-        <v>0.04</v>
+        <v>0.17</v>
       </c>
       <c r="AY51" t="n">
-        <v>0.013</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>#43 L. SÁNCHEZ (Per Game)</t>
+          <t>#44 F. TORREBLANCA (Per Game)</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -8337,10 +8337,10 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -8361,10 +8361,10 @@
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
         <v>0</v>
@@ -8391,13 +8391,13 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
@@ -8421,27 +8421,27 @@
         <v>0</v>
       </c>
       <c r="AL52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM52" t="n">
         <v>0</v>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AR52" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AS52" t="n">
         <v>0</v>
@@ -8453,26 +8453,26 @@
         <v>0</v>
       </c>
       <c r="AV52" t="n">
-        <v>0.277</v>
+        <v>0</v>
       </c>
       <c r="AW52" t="n">
         <v>0</v>
       </c>
       <c r="AX52" t="n">
-        <v>0.171</v>
+        <v>0</v>
       </c>
       <c r="AY52" t="n">
-        <v>0.073</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>#44 F. TORREBLANCA (Per Game)</t>
+          <t>#45 G. NASPLER (Per Game)</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -8481,7 +8481,7 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -8505,7 +8505,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -8514,10 +8514,10 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -8544,7 +8544,7 @@
         <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -8587,11 +8587,11 @@
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:16</t>
         </is>
       </c>
       <c r="AO53" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP53" t="n">
         <v>0</v>
@@ -8603,7 +8603,7 @@
         <v>0</v>
       </c>
       <c r="AS53" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AT53" t="n">
         <v>0</v>
@@ -8612,7 +8612,7 @@
         <v>0</v>
       </c>
       <c r="AV53" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="AW53" t="n">
         <v>0</v>
@@ -8627,11 +8627,11 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>#45 G. NASPLER (Per Game)</t>
+          <t>#46 L. BERGSENG (Per Game)</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -8640,7 +8640,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -8664,7 +8664,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
@@ -8673,10 +8673,10 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -8703,7 +8703,7 @@
         <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -8746,11 +8746,11 @@
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>01:16</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP54" t="n">
         <v>0</v>
@@ -8762,7 +8762,7 @@
         <v>0</v>
       </c>
       <c r="AS54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AT54" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
         <v>0</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.172</v>
+        <v>0</v>
       </c>
       <c r="AW54" t="n">
         <v>0</v>
@@ -8786,65 +8786,65 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>#46 L. BERGSENG (Per Game)</t>
+          <t>#47 A. IZAW-BOLAVIE (Per Game)</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>7</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="R55" t="n">
         <v>1</v>
       </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -8859,13 +8859,13 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AB55" t="n">
         <v>0</v>
@@ -8905,23 +8905,23 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="AO55" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AT55" t="n">
         <v>0</v>
@@ -8930,13 +8930,13 @@
         <v>0</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>0.172</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AY55" t="n">
         <v>0</v>
@@ -8945,71 +8945,71 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>#47 A. IZAW-BOLAVIE (Per Game)</t>
+          <t>#55 D. PÉREZ (Per Game)</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C56" t="n">
-        <v>0.286</v>
+        <v>2.895</v>
       </c>
       <c r="D56" t="n">
-        <v>0.143</v>
+        <v>0.632</v>
       </c>
       <c r="E56" t="n">
-        <v>0.429</v>
+        <v>2.421</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>0.421</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1.684</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>0.474</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>3.158</v>
       </c>
       <c r="K56" t="n">
-        <v>0.143</v>
+        <v>1.105</v>
       </c>
       <c r="L56" t="n">
-        <v>0.286</v>
+        <v>0.263</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>0.316</v>
       </c>
       <c r="N56" t="n">
-        <v>0.143</v>
+        <v>0.211</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0.143</v>
+        <v>1.737</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.143</v>
+        <v>1.737</v>
       </c>
       <c r="R56" t="n">
-        <v>1</v>
+        <v>1.579</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1.579</v>
       </c>
       <c r="T56" t="n">
-        <v>-4</v>
+        <v>58</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="W56" t="n">
         <v>0</v>
@@ -9018,337 +9018,337 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.143</v>
+        <v>0.579</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.429</v>
+        <v>1.211</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.333</v>
+        <v>0.478</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>0.842</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>0.842</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH56" t="n">
         <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="AJ56" t="n">
         <v>0</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>0.421</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>1.579</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>0.267</v>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AO56" t="n">
-        <v>0.571</v>
+        <v>6.051</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.333</v>
+        <v>0.308</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.333</v>
+        <v>0.336</v>
       </c>
       <c r="AR56" t="n">
-        <v>0.5</v>
+        <v>0.478</v>
       </c>
       <c r="AS56" t="n">
-        <v>0.25</v>
+        <v>0.287</v>
       </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>1.818</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.143</v>
+        <v>0.187</v>
       </c>
       <c r="AW56" t="n">
-        <v>0.173</v>
+        <v>0.02</v>
       </c>
       <c r="AX56" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AY56" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>#55 D. PÉREZ (Per Game)</t>
+          <t>#99 A. PLUMMER (Per Game)</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C57" t="n">
-        <v>2.533</v>
+        <v>9</v>
       </c>
       <c r="D57" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E57" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="K57" t="n">
         <v>0.333</v>
       </c>
-      <c r="G57" t="n">
-        <v>1.533</v>
-      </c>
-      <c r="H57" t="n">
+      <c r="L57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M57" t="n">
         <v>0.333</v>
       </c>
-      <c r="I57" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0.267</v>
-      </c>
       <c r="N57" t="n">
-        <v>0.133</v>
+        <v>0.5</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>1.733</v>
+        <v>0.833</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.733</v>
+        <v>0.833</v>
       </c>
       <c r="R57" t="n">
-        <v>1.667</v>
+        <v>2.833</v>
       </c>
       <c r="S57" t="n">
-        <v>1.533</v>
+        <v>0.833</v>
       </c>
       <c r="T57" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="U57" t="n">
-        <v>0.333</v>
+        <v>1.333</v>
       </c>
       <c r="V57" t="n">
-        <v>0.267</v>
+        <v>1.833</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.2</v>
+        <v>2.333</v>
       </c>
       <c r="AA57" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB57" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>1</v>
-      </c>
       <c r="AD57" t="n">
-        <v>0.267</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
         <v>0.667</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.067</v>
+        <v>1.167</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AK57" t="n">
-        <v>0.333</v>
+        <v>2</v>
       </c>
       <c r="AL57" t="n">
-        <v>1.467</v>
+        <v>4.167</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.227</v>
+        <v>0.48</v>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AO57" t="n">
-        <v>5.872</v>
+        <v>8.827</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.28</v>
+        <v>0.511</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.306</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR57" t="n">
-        <v>0.431</v>
+        <v>1.02</v>
       </c>
       <c r="AS57" t="n">
-        <v>0.295</v>
+        <v>0.094</v>
       </c>
       <c r="AT57" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.205</v>
       </c>
       <c r="AU57" t="n">
-        <v>1.923</v>
+        <v>0.2</v>
       </c>
       <c r="AV57" t="n">
-        <v>0.193</v>
+        <v>0.238</v>
       </c>
       <c r="AW57" t="n">
-        <v>0.021</v>
+        <v>0.033</v>
       </c>
       <c r="AX57" t="n">
-        <v>0.097</v>
+        <v>0.022</v>
       </c>
       <c r="AY57" t="n">
-        <v>0.122</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>#99 A. PLUMMER (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>2.167</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>5.333</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0.333</v>
+        <v>1.562</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5</v>
+        <v>1.875</v>
       </c>
       <c r="M58" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0.833</v>
+        <v>0.969</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>2.833</v>
+        <v>0.344</v>
       </c>
       <c r="S58" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>1.833</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.333</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
         <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
@@ -9357,222 +9357,222 @@
         <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.167</v>
+        <v>0</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="AK58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL58" t="n">
-        <v>4.167</v>
+        <v>0</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO58" t="n">
-        <v>8.827</v>
+        <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>0.511</v>
+        <v>0</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.5629999999999999</v>
+        <v>0</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AS58" t="n">
-        <v>0.094</v>
+        <v>0</v>
       </c>
       <c r="AT58" t="n">
-        <v>0.205</v>
+        <v>0</v>
       </c>
       <c r="AU58" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AV58" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="AW58" t="n">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="AX58" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="AY58" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>85.96899999999999</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>18.781</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>36.781</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>9.843999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>28.406</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>18.875</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>24.938</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>17.812</v>
       </c>
       <c r="K59" t="n">
-        <v>1.571</v>
+        <v>23.656</v>
       </c>
       <c r="L59" t="n">
-        <v>1.893</v>
+        <v>11.719</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>6.562</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>5.969</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>0.786</v>
+        <v>15.531</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>14.562</v>
       </c>
       <c r="R59" t="n">
+        <v>23.844</v>
+      </c>
+      <c r="S59" t="n">
+        <v>24.531</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3015</v>
+      </c>
+      <c r="U59" t="n">
+        <v>11.656</v>
+      </c>
+      <c r="V59" t="n">
+        <v>11.938</v>
+      </c>
+      <c r="W59" t="n">
+        <v>7.469</v>
+      </c>
+      <c r="X59" t="n">
+        <v>4.562</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>31.406</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>43.094</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>4.062</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>11.812</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>2.188</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>6.812</v>
+      </c>
+      <c r="AG59" t="n">
         <v>0.321</v>
       </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>0</v>
-      </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>2.625</v>
       </c>
       <c r="AI59" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>7.219</v>
       </c>
       <c r="AL59" t="n">
-        <v>0</v>
+        <v>20.906</v>
       </c>
       <c r="AM59" t="n">
-        <v>0</v>
+        <v>0.345</v>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:46</t>
         </is>
       </c>
       <c r="AO59" t="n">
-        <v>0</v>
+        <v>91.691</v>
       </c>
       <c r="AP59" t="n">
-        <v>0</v>
+        <v>0.515</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AR59" t="n">
-        <v>0</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AS59" t="n">
-        <v>0</v>
+        <v>0.169</v>
       </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="AU59" t="n">
-        <v>0</v>
+        <v>1.147</v>
       </c>
       <c r="AV59" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW59" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AX59" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="AY59" t="n">
         <v>0</v>
@@ -9581,477 +9581,159 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>91.03100000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>23.094</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>41.906</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>8.811999999999999</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>25.281</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>18.406</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>24.406</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>15.906</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>26.062</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>13.438</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>5.844</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>15.719</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>14.594</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>24.812</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>23.594</v>
       </c>
       <c r="T60" t="n">
-        <v>66</v>
+        <v>3274</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>11.906</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>13.188</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>5.688</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>3.562</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>34.844</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>48.781</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>10.469</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>0.382</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>2.656</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>7.062</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>0.376</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI60" t="n">
-        <v>0</v>
+        <v>4.312</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="AK60" t="n">
-        <v>0</v>
+        <v>7.062</v>
       </c>
       <c r="AL60" t="n">
-        <v>0</v>
+        <v>20.969</v>
       </c>
       <c r="AM60" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:46</t>
         </is>
       </c>
       <c r="AO60" t="n">
-        <v>0.786</v>
+        <v>93.645</v>
       </c>
       <c r="AP60" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0</v>
+        <v>0.584</v>
       </c>
       <c r="AR60" t="n">
-        <v>0</v>
+        <v>0.972</v>
       </c>
       <c r="AS60" t="n">
-        <v>0</v>
+        <v>0.168</v>
       </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>0.274</v>
       </c>
       <c r="AU60" t="n">
-        <v>0</v>
+        <v>1.012</v>
       </c>
       <c r="AV60" t="n">
-        <v>0</v>
+        <v>0.204</v>
       </c>
       <c r="AW60" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX60" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AY60" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>28</v>
-      </c>
-      <c r="C61" t="n">
-        <v>84.75</v>
-      </c>
-      <c r="D61" t="n">
-        <v>18.714</v>
-      </c>
-      <c r="E61" t="n">
-        <v>36.821</v>
-      </c>
-      <c r="F61" t="n">
-        <v>9.643000000000001</v>
-      </c>
-      <c r="G61" t="n">
-        <v>28.107</v>
-      </c>
-      <c r="H61" t="n">
-        <v>18.393</v>
-      </c>
-      <c r="I61" t="n">
-        <v>24.321</v>
-      </c>
-      <c r="J61" t="n">
-        <v>17.786</v>
-      </c>
-      <c r="K61" t="n">
-        <v>23.393</v>
-      </c>
-      <c r="L61" t="n">
-        <v>11.571</v>
-      </c>
-      <c r="M61" t="n">
-        <v>6.286</v>
-      </c>
-      <c r="N61" t="n">
-        <v>5.929</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>15.464</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>14.679</v>
-      </c>
-      <c r="R61" t="n">
-        <v>23.786</v>
-      </c>
-      <c r="S61" t="n">
-        <v>24.214</v>
-      </c>
-      <c r="T61" t="n">
-        <v>2581</v>
-      </c>
-      <c r="U61" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="V61" t="n">
-        <v>11.821</v>
-      </c>
-      <c r="W61" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="X61" t="n">
-        <v>4.357</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>31.107</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>42.857</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>3.857</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>11.429</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>0.338</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>2.143</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>6.857</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>7.071</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>7.143</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>21.036</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>200:53</t>
-        </is>
-      </c>
-      <c r="AO61" t="n">
-        <v>91.09399999999999</v>
-      </c>
-      <c r="AP61" t="n">
-        <v>0.511</v>
-      </c>
-      <c r="AQ61" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AR61" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AS61" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AT61" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="AU61" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AV61" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW61" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="AX61" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="AY61" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>28</v>
-      </c>
-      <c r="C62" t="n">
-        <v>91.071</v>
-      </c>
-      <c r="D62" t="n">
-        <v>23.214</v>
-      </c>
-      <c r="E62" t="n">
-        <v>42.036</v>
-      </c>
-      <c r="F62" t="n">
-        <v>8.786</v>
-      </c>
-      <c r="G62" t="n">
-        <v>25</v>
-      </c>
-      <c r="H62" t="n">
-        <v>18.286</v>
-      </c>
-      <c r="I62" t="n">
-        <v>24.143</v>
-      </c>
-      <c r="J62" t="n">
-        <v>16.036</v>
-      </c>
-      <c r="K62" t="n">
-        <v>26.071</v>
-      </c>
-      <c r="L62" t="n">
-        <v>13.464</v>
-      </c>
-      <c r="M62" t="n">
-        <v>8.356999999999999</v>
-      </c>
-      <c r="N62" t="n">
-        <v>5.714</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>15.536</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>14.357</v>
-      </c>
-      <c r="R62" t="n">
-        <v>24.464</v>
-      </c>
-      <c r="S62" t="n">
-        <v>23.607</v>
-      </c>
-      <c r="T62" t="n">
-        <v>2896</v>
-      </c>
-      <c r="U62" t="n">
-        <v>12.429</v>
-      </c>
-      <c r="V62" t="n">
-        <v>13.286</v>
-      </c>
-      <c r="W62" t="n">
-        <v>5.143</v>
-      </c>
-      <c r="X62" t="n">
-        <v>3.286</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>34.786</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>49</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>3.893</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>10.286</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>2.821</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>6.893</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>1.786</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>0.397</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL62" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="AM62" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>200:53</t>
-        </is>
-      </c>
-      <c r="AO62" t="n">
-        <v>93.194</v>
-      </c>
-      <c r="AP62" t="n">
-        <v>0.543</v>
-      </c>
-      <c r="AQ62" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="AR62" t="n">
-        <v>0.977</v>
-      </c>
-      <c r="AS62" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AT62" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="AU62" t="n">
-        <v>1.032</v>
-      </c>
-      <c r="AV62" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="AW62" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="AX62" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="AY62" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_BAXI Manresa.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_BAXI Manresa.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2559.12</v>
+        <v>2726.08</v>
       </c>
       <c r="C2" t="n">
-        <v>2562.88</v>
+        <v>2729.72</v>
       </c>
       <c r="D2" t="n">
-        <v>107.3401797977276</v>
+        <v>107.4102838386355</v>
       </c>
       <c r="E2" t="n">
-        <v>113.6611936571357</v>
+        <v>112.8320853420864</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5146212847555129</v>
+        <v>0.5130161579892281</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1693863918312816</v>
+        <v>0.1669288921293987</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3101736972704714</v>
+        <v>0.3113354037267081</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2895493767976989</v>
+        <v>0.2899461400359066</v>
       </c>
       <c r="J2" t="n">
-        <v>373</v>
+        <v>401</v>
       </c>
       <c r="K2" t="n">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="L2" t="n">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="M2" t="n">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="N2" t="n">
-        <v>1005</v>
+        <v>1079</v>
       </c>
       <c r="O2" t="n">
-        <v>1379</v>
+        <v>1484</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6610738255033557</v>
+        <v>0.6660682226211849</v>
       </c>
       <c r="Q2" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="R2" t="n">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1812080536912752</v>
+        <v>0.1795332136445242</v>
       </c>
       <c r="T2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="U2" t="n">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1045062320230105</v>
+        <v>0.1018850987432675</v>
       </c>
       <c r="W2" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="X2" t="n">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1150527325023969</v>
+        <v>0.1144524236983842</v>
       </c>
       <c r="Z2" t="n">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="AA2" t="n">
-        <v>669</v>
+        <v>719</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3207094918504315</v>
+        <v>0.3227109515260323</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.728788977519942</v>
+        <v>0.727088948787062</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3439153439153439</v>
+        <v>0.3475</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3211009174311927</v>
+        <v>0.3215859030837004</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.35</v>
+        <v>0.3450980392156863</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3452914798206278</v>
+        <v>0.3393602225312934</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.457577955039884</v>
+        <v>1.454177897574124</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.6422018348623854</v>
+        <v>0.6431718061674009</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.03960396039604</v>
+        <v>1.02258726899384</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7415506958250497</v>
+        <v>0.7509363295880149</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.018666666666667</v>
+        <v>1.019950124688279</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.636986301369863</v>
+        <v>1.624242424242424</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.146881287726358</v>
+        <v>1.151340996168582</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.197183098591549</v>
+        <v>4.268199233716475</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.344064386317908</v>
+        <v>5.419540229885057</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79.9725</v>
+        <v>80.17882352941176</v>
       </c>
       <c r="C3" t="n">
-        <v>80.09</v>
+        <v>80.28588235294119</v>
       </c>
       <c r="D3" t="n">
-        <v>107.3401797977276</v>
+        <v>107.4102838386355</v>
       </c>
       <c r="E3" t="n">
-        <v>113.6611936571357</v>
+        <v>112.8320853420864</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5146212847555129</v>
+        <v>0.5130161579892279</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1693863918312816</v>
+        <v>0.1669288921293987</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3101736972704714</v>
+        <v>0.3113354037267081</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2895493767976989</v>
+        <v>0.2899461400359066</v>
       </c>
       <c r="J3" t="n">
-        <v>11.65625</v>
+        <v>11.79411764705882</v>
       </c>
       <c r="K3" t="n">
-        <v>11.9375</v>
+        <v>12.02941176470588</v>
       </c>
       <c r="L3" t="n">
-        <v>7.46875</v>
+        <v>7.882352941176471</v>
       </c>
       <c r="M3" t="n">
-        <v>14.5625</v>
+        <v>14.41176470588235</v>
       </c>
       <c r="N3" t="n">
-        <v>31.40625</v>
+        <v>31.73529411764706</v>
       </c>
       <c r="O3" t="n">
-        <v>43.09375</v>
+        <v>43.64705882352941</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6610738255033557</v>
+        <v>0.6660682226211849</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.0625</v>
+        <v>4.088235294117647</v>
       </c>
       <c r="R3" t="n">
-        <v>11.8125</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1812080536912752</v>
+        <v>0.1795332136445242</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1875</v>
+        <v>2.147058823529412</v>
       </c>
       <c r="U3" t="n">
-        <v>6.8125</v>
+        <v>6.676470588235294</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1045062320230105</v>
+        <v>0.1018850987432675</v>
       </c>
       <c r="W3" t="n">
-        <v>2.625</v>
+        <v>2.588235294117647</v>
       </c>
       <c r="X3" t="n">
         <v>7.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1150527325023969</v>
+        <v>0.1144524236983842</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.21875</v>
+        <v>7.176470588235294</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.90625</v>
+        <v>21.14705882352941</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3207094918504315</v>
+        <v>0.3227109515260324</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.728788977519942</v>
+        <v>0.727088948787062</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3439153439153439</v>
+        <v>0.3475</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3211009174311927</v>
+        <v>0.3215859030837004</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.35</v>
+        <v>0.3450980392156863</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3452914798206278</v>
+        <v>0.3393602225312934</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.457577955039884</v>
+        <v>1.454177897574124</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.6422018348623854</v>
+        <v>0.6431718061674009</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.03960396039604</v>
+        <v>1.02258726899384</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7415506958250497</v>
+        <v>0.750936329588015</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.018666666666667</v>
+        <v>1.019950124688279</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.636986301369863</v>
+        <v>1.624242424242424</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.146881287726358</v>
+        <v>1.151340996168582</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.197183098591549</v>
+        <v>4.268199233716475</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.344064386317908</v>
+        <v>5.419540229885057</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2566.640000000001</v>
+        <v>2733.360000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>2562.88</v>
+        <v>2729.72</v>
       </c>
       <c r="D4" t="n">
-        <v>113.6611936571357</v>
+        <v>112.8320853420864</v>
       </c>
       <c r="E4" t="n">
-        <v>107.3401797977276</v>
+        <v>107.4102838386355</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5404651162790698</v>
+        <v>0.5387308533916849</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1678546638902237</v>
+        <v>0.1679583312364753</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3622577927548442</v>
+        <v>0.3531274742676168</v>
       </c>
       <c r="I4" t="n">
-        <v>0.273953488372093</v>
+        <v>0.2704595185995624</v>
       </c>
       <c r="J4" t="n">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="K4" t="n">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="L4" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="M4" t="n">
-        <v>467</v>
+        <v>493</v>
       </c>
       <c r="N4" t="n">
-        <v>1115</v>
+        <v>1170</v>
       </c>
       <c r="O4" t="n">
-        <v>1561</v>
+        <v>1637</v>
       </c>
       <c r="P4" t="n">
-        <v>0.726046511627907</v>
+        <v>0.7164113785557987</v>
       </c>
       <c r="Q4" t="n">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="R4" t="n">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1558139534883721</v>
+        <v>0.1597374179431072</v>
       </c>
       <c r="T4" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="U4" t="n">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1051162790697674</v>
+        <v>0.1041575492341357</v>
       </c>
       <c r="W4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="X4" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0641860465116279</v>
+        <v>0.06695842450765864</v>
       </c>
       <c r="Z4" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="AA4" t="n">
-        <v>671</v>
+        <v>711</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.312093023255814</v>
+        <v>0.3111597374179431</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7147220525351252</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.382089552238806</v>
+        <v>0.3917808219178082</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3761061946902655</v>
+        <v>0.3865546218487395</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4057971014492754</v>
+        <v>0.392156862745098</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3368107302533532</v>
+        <v>0.3319268635724332</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.428571428571429</v>
+        <v>1.42944410507025</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.7522123893805309</v>
+        <v>0.773109243697479</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.045735475896168</v>
+        <v>1.027777777777778</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7665995975855131</v>
+        <v>0.7720306513409961</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.9813953488372092</v>
+        <v>0.9775784753363229</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.596491228070176</v>
+        <v>1.601694915254237</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.011928429423459</v>
+        <v>1.00187265917603</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.274353876739562</v>
+        <v>4.279026217228465</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.286282306163022</v>
+        <v>5.280898876404494</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80.20750000000002</v>
+        <v>80.39294117647061</v>
       </c>
       <c r="C5" t="n">
-        <v>80.09</v>
+        <v>80.28588235294119</v>
       </c>
       <c r="D5" t="n">
-        <v>113.6611936571357</v>
+        <v>112.8320853420864</v>
       </c>
       <c r="E5" t="n">
-        <v>107.3401797977276</v>
+        <v>107.4102838386355</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5404651162790698</v>
+        <v>0.5387308533916849</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1678546638902237</v>
+        <v>0.1679583312364753</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3622577927548442</v>
+        <v>0.3531274742676168</v>
       </c>
       <c r="I5" t="n">
-        <v>0.273953488372093</v>
+        <v>0.2704595185995624</v>
       </c>
       <c r="J5" t="n">
-        <v>11.90625</v>
+        <v>11.85294117647059</v>
       </c>
       <c r="K5" t="n">
-        <v>13.1875</v>
+        <v>12.82352941176471</v>
       </c>
       <c r="L5" t="n">
-        <v>5.6875</v>
+        <v>5.558823529411764</v>
       </c>
       <c r="M5" t="n">
-        <v>14.59375</v>
+        <v>14.5</v>
       </c>
       <c r="N5" t="n">
-        <v>34.84375</v>
+        <v>34.41176470588236</v>
       </c>
       <c r="O5" t="n">
-        <v>48.78125</v>
+        <v>48.14705882352941</v>
       </c>
       <c r="P5" t="n">
-        <v>0.726046511627907</v>
+        <v>0.7164113785557987</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>4.205882352941177</v>
       </c>
       <c r="R5" t="n">
-        <v>10.46875</v>
+        <v>10.73529411764706</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1558139534883721</v>
+        <v>0.1597374179431072</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65625</v>
+        <v>2.705882352941177</v>
       </c>
       <c r="U5" t="n">
-        <v>7.0625</v>
+        <v>7</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1051162790697674</v>
+        <v>0.1041575492341357</v>
       </c>
       <c r="W5" t="n">
-        <v>1.75</v>
+        <v>1.764705882352941</v>
       </c>
       <c r="X5" t="n">
-        <v>4.3125</v>
+        <v>4.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0641860465116279</v>
+        <v>0.06695842450765864</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.0625</v>
+        <v>6.941176470588236</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.96875</v>
+        <v>20.91176470588235</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.312093023255814</v>
+        <v>0.3111597374179431</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7147220525351252</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.382089552238806</v>
+        <v>0.3917808219178083</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3761061946902655</v>
+        <v>0.3865546218487395</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4057971014492754</v>
+        <v>0.392156862745098</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3368107302533532</v>
+        <v>0.3319268635724332</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.428571428571429</v>
+        <v>1.42944410507025</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.7522123893805309</v>
+        <v>0.773109243697479</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.045735475896168</v>
+        <v>1.027777777777778</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7665995975855131</v>
+        <v>0.7720306513409961</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.9813953488372092</v>
+        <v>0.9775784753363229</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.596491228070176</v>
+        <v>1.601694915254237</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.011928429423459</v>
+        <v>1.00187265917603</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.274353876739562</v>
+        <v>4.279026217228465</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.286282306163022</v>
+        <v>5.280898876404494</v>
       </c>
     </row>
     <row r="7">
@@ -1419,16 +1419,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D8" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E8" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1437,64 +1437,64 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I8" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L8" t="n">
         <v>31</v>
       </c>
       <c r="M8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>23</v>
+      </c>
+      <c r="R8" t="n">
+        <v>77</v>
+      </c>
+      <c r="S8" t="n">
+        <v>42</v>
+      </c>
+      <c r="T8" t="n">
+        <v>224</v>
+      </c>
+      <c r="U8" t="n">
+        <v>22</v>
+      </c>
+      <c r="V8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W8" t="n">
+        <v>6</v>
+      </c>
+      <c r="X8" t="n">
         <v>4</v>
       </c>
-      <c r="N8" t="n">
-        <v>53</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>20</v>
-      </c>
-      <c r="R8" t="n">
-        <v>72</v>
-      </c>
-      <c r="S8" t="n">
-        <v>39</v>
-      </c>
-      <c r="T8" t="n">
-        <v>213</v>
-      </c>
-      <c r="U8" t="n">
-        <v>20</v>
-      </c>
-      <c r="V8" t="n">
-        <v>23</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
       <c r="Y8" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="Z8" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.772</v>
+        <v>0.771</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1534,38 +1534,38 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>442:42</t>
+          <t>464:58</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>112.4</v>
+        <v>121.16</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.879</v>
+        <v>0.886</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.828</v>
+        <v>0.83</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.361</v>
+        <v>1.345</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.178</v>
+        <v>0.19</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.5</v>
+        <v>0.478</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.111</v>
+        <v>0.114</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.074</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.112</v>
+        <v>0.116</v>
       </c>
       <c r="AY8" t="n">
         <v>0.012</v>
@@ -1718,7 +1718,7 @@
         <v>2.31</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.27</v>
+        <v>0.269</v>
       </c>
       <c r="AW9" t="n">
         <v>0.041</v>
@@ -1727,7 +1727,7 @@
         <v>0.091</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.078</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="10">
@@ -1737,91 +1737,91 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" t="n">
+        <v>82</v>
+      </c>
+      <c r="D10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" t="n">
+        <v>34</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>28</v>
+      </c>
+      <c r="H10" t="n">
+        <v>31</v>
+      </c>
+      <c r="I10" t="n">
+        <v>43</v>
+      </c>
+      <c r="J10" t="n">
+        <v>16</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" t="n">
+        <v>16</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>16</v>
+      </c>
+      <c r="R10" t="n">
+        <v>22</v>
+      </c>
+      <c r="S10" t="n">
+        <v>30</v>
+      </c>
+      <c r="T10" t="n">
+        <v>75</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>14</v>
+      </c>
+      <c r="W10" t="n">
+        <v>16</v>
+      </c>
+      <c r="X10" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>64</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC10" t="n">
         <v>8</v>
       </c>
-      <c r="C10" t="n">
-        <v>56</v>
-      </c>
-      <c r="D10" t="n">
-        <v>11</v>
-      </c>
-      <c r="E10" t="n">
-        <v>22</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" t="n">
-        <v>26</v>
-      </c>
-      <c r="H10" t="n">
-        <v>22</v>
-      </c>
-      <c r="I10" t="n">
-        <v>28</v>
-      </c>
-      <c r="J10" t="n">
-        <v>15</v>
-      </c>
-      <c r="K10" t="n">
-        <v>9</v>
-      </c>
-      <c r="L10" t="n">
-        <v>10</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>14</v>
-      </c>
-      <c r="R10" t="n">
-        <v>18</v>
-      </c>
-      <c r="S10" t="n">
-        <v>20</v>
-      </c>
-      <c r="T10" t="n">
-        <v>46</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>12</v>
-      </c>
-      <c r="X10" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>5</v>
-      </c>
       <c r="AD10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -1833,57 +1833,57 @@
         <v>0.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.154</v>
+        <v>0.214</v>
       </c>
       <c r="AK10" t="n">
         <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.154</v>
+        <v>0.143</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>138:11</t>
+          <t>167:15</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>74.31999999999999</v>
+        <v>96.92</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.354</v>
+        <v>0.411</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.464</v>
+        <v>0.507</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.753</v>
+        <v>0.846</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.188</v>
+        <v>0.165</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.458</v>
+        <v>0.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.071</v>
+        <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.236</v>
+        <v>0.253</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.077</v>
+        <v>0.101</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="AY10" t="n">
         <v>0.017</v>
@@ -2045,7 +2045,7 @@
         <v>0.063</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="12">
@@ -2055,156 +2055,156 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="H12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J12" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="K12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M12" t="n">
         <v>23</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>60</v>
+      </c>
+      <c r="R12" t="n">
+        <v>60</v>
+      </c>
+      <c r="S12" t="n">
         <v>58</v>
       </c>
-      <c r="Q12" t="n">
-        <v>58</v>
-      </c>
-      <c r="R12" t="n">
-        <v>55</v>
-      </c>
-      <c r="S12" t="n">
-        <v>56</v>
-      </c>
       <c r="T12" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="U12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="V12" t="n">
         <v>31</v>
       </c>
       <c r="W12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z12" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.618</v>
+        <v>0.614</v>
       </c>
       <c r="AB12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.412</v>
+        <v>0.405</v>
       </c>
       <c r="AE12" t="n">
         <v>3</v>
       </c>
       <c r="AF12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="AH12" t="n">
         <v>8</v>
       </c>
       <c r="AI12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.364</v>
+        <v>0.32</v>
       </c>
       <c r="AK12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="AL12" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.343</v>
+        <v>0.345</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>471:28</t>
+          <t>512:09</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>283.36</v>
+        <v>308</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.478</v>
+        <v>0.467</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.805</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.205</v>
+        <v>0.195</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.16</v>
+        <v>0.164</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.362</v>
+        <v>2.367</v>
       </c>
       <c r="AV12" t="n">
         <v>0.263</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.06</v>
+        <v>0.057</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.163</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="13">
@@ -2214,37 +2214,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" t="n">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="D13" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E13" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F13" t="n">
+        <v>87</v>
+      </c>
+      <c r="G13" t="n">
+        <v>218</v>
+      </c>
+      <c r="H13" t="n">
         <v>84</v>
       </c>
-      <c r="G13" t="n">
-        <v>205</v>
-      </c>
-      <c r="H13" t="n">
-        <v>79</v>
-      </c>
       <c r="I13" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="J13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K13" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="L13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M13" t="n">
         <v>23</v>
@@ -2256,40 +2256,40 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q13" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="S13" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="T13" t="n">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="U13" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="V13" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="W13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="Z13" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.774</v>
+        <v>0.779</v>
       </c>
       <c r="AB13" t="n">
         <v>8</v>
@@ -2313,57 +2313,57 @@
         <v>18</v>
       </c>
       <c r="AI13" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.367</v>
+        <v>0.353</v>
       </c>
       <c r="AK13" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AL13" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.423</v>
+        <v>0.413</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>781:08</t>
+          <t>825:23</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>373</v>
+        <v>391.64</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.576</v>
+        <v>0.569</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.617</v>
+        <v>0.612</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.129</v>
+        <v>1.121</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.266</v>
+        <v>0.269</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.75</v>
+        <v>0.788</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.209</v>
+        <v>0.207</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.18</v>
+        <v>0.187</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="14">
@@ -2373,40 +2373,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C14" t="n">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E14" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H14" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I14" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="J14" t="n">
         <v>32</v>
       </c>
       <c r="K14" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L14" t="n">
         <v>21</v>
       </c>
       <c r="M14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N14" t="n">
         <v>19</v>
@@ -2415,114 +2415,114 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Q14" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="R14" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S14" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="T14" t="n">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="U14" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="V14" t="n">
         <v>31</v>
       </c>
       <c r="W14" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="X14" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="Y14" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="Z14" t="n">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.771</v>
+        <v>0.781</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.295</v>
+        <v>0.304</v>
       </c>
       <c r="AE14" t="n">
         <v>8</v>
       </c>
       <c r="AF14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.421</v>
+        <v>0.4</v>
       </c>
       <c r="AH14" t="n">
         <v>8</v>
       </c>
       <c r="AI14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.421</v>
+        <v>0.4</v>
       </c>
       <c r="AK14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL14" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.259</v>
+        <v>0.268</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>566:13</t>
+          <t>594:00</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>295.88</v>
+        <v>311.96</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.48</v>
+        <v>0.491</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.577</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.958</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.172</v>
+        <v>0.17</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.43</v>
+        <v>0.436</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.627</v>
+        <v>0.604</v>
       </c>
       <c r="AV14" t="n">
         <v>0.229</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.151</v>
+        <v>0.153</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.039</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="15">
@@ -2532,22 +2532,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C15" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E15" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H15" t="n">
         <v>21</v>
@@ -2559,40 +2559,40 @@
         <v>25</v>
       </c>
       <c r="K15" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Q15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R15" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="S15" t="n">
         <v>28</v>
       </c>
       <c r="T15" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="U15" t="n">
         <v>11</v>
       </c>
       <c r="V15" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="W15" t="n">
         <v>13</v>
@@ -2601,22 +2601,22 @@
         <v>6</v>
       </c>
       <c r="Y15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Z15" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.694</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="AB15" t="n">
         <v>5</v>
       </c>
       <c r="AC15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.312</v>
+        <v>0.294</v>
       </c>
       <c r="AE15" t="n">
         <v>4</v>
@@ -2628,60 +2628,60 @@
         <v>0.444</v>
       </c>
       <c r="AH15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.346</v>
+        <v>0.357</v>
       </c>
       <c r="AK15" t="n">
         <v>30</v>
       </c>
       <c r="AL15" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.366</v>
+        <v>0.345</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>652:06</t>
+          <t>686:05</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>209.88</v>
+        <v>224.88</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.519</v>
+        <v>0.508</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.542</v>
+        <v>0.53</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.996</v>
+        <v>0.965</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.081</v>
+        <v>0.089</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.116</v>
+        <v>0.109</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.471</v>
+        <v>1.25</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.141</v>
+        <v>0.143</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.047</v>
+        <v>0.046</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.081</v>
+        <v>0.082</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="16">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C16" t="n">
         <v>84</v>
@@ -2700,13 +2700,13 @@
         <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F16" t="n">
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H16" t="n">
         <v>10</v>
@@ -2718,10 +2718,10 @@
         <v>11</v>
       </c>
       <c r="K16" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="L16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M16" t="n">
         <v>18</v>
@@ -2733,19 +2733,19 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R16" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T16" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="U16" t="n">
         <v>13</v>
@@ -2763,10 +2763,10 @@
         <v>34</v>
       </c>
       <c r="Z16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.654</v>
+        <v>0.642</v>
       </c>
       <c r="AB16" t="n">
         <v>5</v>
@@ -2790,54 +2790,54 @@
         <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.077</v>
+        <v>0.067</v>
       </c>
       <c r="AK16" t="n">
         <v>3</v>
       </c>
       <c r="AL16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>333:23</t>
+          <t>367:33</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>100.48</v>
+        <v>106.48</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.487</v>
+        <v>0.457</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.503</v>
+        <v>0.475</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.836</v>
+        <v>0.789</v>
       </c>
       <c r="AS16" t="n">
         <v>0.169</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.132</v>
+        <v>0.123</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.647</v>
+        <v>0.611</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.132</v>
+        <v>0.126</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.054</v>
+        <v>0.055</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.153</v>
+        <v>0.165</v>
       </c>
       <c r="AY16" t="n">
         <v>0.012</v>
@@ -2999,7 +2999,7 @@
         <v>0.127</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="18">
@@ -3009,16 +3009,16 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" t="n">
+        <v>21</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
         <v>13</v>
-      </c>
-      <c r="C18" t="n">
-        <v>19</v>
-      </c>
-      <c r="D18" t="n">
-        <v>6</v>
-      </c>
-      <c r="E18" t="n">
-        <v>12</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -3036,13 +3036,13 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
         <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
         <v>7</v>
@@ -3051,13 +3051,13 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S18" t="n">
         <v>7</v>
@@ -3078,13 +3078,13 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.632</v>
+        <v>0.65</v>
       </c>
       <c r="AB18" t="n">
         <v>1</v>
@@ -3124,38 +3124,38 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>57:13</t>
+          <t>66:51</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>23.72</v>
+        <v>27.72</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.5</v>
+        <v>0.538</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.536</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.801</v>
+        <v>0.758</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.253</v>
+        <v>0.325</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.583</v>
+        <v>0.538</v>
       </c>
       <c r="AU18" t="n">
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.182</v>
+        <v>0.181</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.093</v>
+        <v>0.079</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.095</v>
+        <v>0.097</v>
       </c>
       <c r="AY18" t="n">
         <v>0</v>
@@ -3168,40 +3168,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H19" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I19" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J19" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K19" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N19" t="n">
         <v>3</v>
@@ -3210,19 +3210,19 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R19" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S19" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="T19" t="n">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="U19" t="n">
         <v>22</v>
@@ -3231,93 +3231,93 @@
         <v>16</v>
       </c>
       <c r="W19" t="n">
+        <v>10</v>
+      </c>
+      <c r="X19" t="n">
         <v>7</v>
       </c>
-      <c r="X19" t="n">
-        <v>6</v>
-      </c>
       <c r="Y19" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="Z19" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.758</v>
+        <v>0.74</v>
       </c>
       <c r="AB19" t="n">
         <v>11</v>
       </c>
       <c r="AC19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.44</v>
+        <v>0.423</v>
       </c>
       <c r="AE19" t="n">
         <v>4</v>
       </c>
       <c r="AF19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.308</v>
+        <v>0.286</v>
       </c>
       <c r="AH19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM19" t="n">
         <v>0.333</v>
       </c>
-      <c r="AK19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0.344</v>
-      </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>304:04</t>
+          <t>343:08</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>144.72</v>
+        <v>161.36</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.505</v>
+        <v>0.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.173</v>
+        <v>0.161</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.301</v>
+        <v>0.302</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.76</v>
+        <v>1.885</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.038</v>
+        <v>0.04</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.103</v>
+        <v>0.101</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.051</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="20">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C20" t="n">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="D20" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E20" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F20" t="n">
         <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H20" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I20" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="J20" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K20" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="L20" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M20" t="n">
         <v>4</v>
@@ -3375,34 +3375,34 @@
         <v>29</v>
       </c>
       <c r="R20" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="S20" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="T20" t="n">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="U20" t="n">
         <v>25</v>
       </c>
       <c r="V20" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="W20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y20" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="Z20" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.848</v>
+        <v>0.837</v>
       </c>
       <c r="AB20" t="n">
         <v>14</v>
@@ -3435,48 +3435,48 @@
         <v>11</v>
       </c>
       <c r="AL20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.367</v>
+        <v>0.344</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>501:19</t>
+          <t>546:58</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>184.68</v>
+        <v>197.2</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.602</v>
+        <v>0.598</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.713</v>
+        <v>0.707</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.202</v>
+        <v>1.207</v>
       </c>
       <c r="AS20" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AV20" t="n">
         <v>0.157</v>
       </c>
-      <c r="AT20" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>1.172</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0.161</v>
-      </c>
       <c r="AW20" t="n">
-        <v>0.106</v>
+        <v>0.11</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.194</v>
+        <v>0.202</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.04</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="21">
@@ -3486,100 +3486,100 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C21" t="n">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="D21" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="E21" t="n">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G21" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H21" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="I21" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="J21" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K21" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M21" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Q21" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R21" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="S21" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="T21" t="n">
-        <v>341</v>
+        <v>370</v>
       </c>
       <c r="U21" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="V21" t="n">
         <v>34</v>
       </c>
       <c r="W21" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="X21" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y21" t="n">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="Z21" t="n">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.731</v>
+        <v>0.735</v>
       </c>
       <c r="AB21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AC21" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.25</v>
+        <v>0.246</v>
       </c>
       <c r="AE21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF21" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.222</v>
+        <v>0.241</v>
       </c>
       <c r="AH21" t="n">
         <v>6</v>
@@ -3591,51 +3591,51 @@
         <v>0.429</v>
       </c>
       <c r="AK21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL21" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.234</v>
+        <v>0.235</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>601:05</t>
+          <t>639:44</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>364.44</v>
+        <v>392.52</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.498</v>
+        <v>0.494</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.569</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.176</v>
+        <v>0.168</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.466</v>
+        <v>0.447</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.875</v>
+        <v>0.879</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.266</v>
+        <v>0.268</v>
       </c>
       <c r="AW21" t="n">
         <v>0.023</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="22">
@@ -3785,16 +3785,16 @@
         <v>0.846</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.251</v>
+        <v>0.25</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.098</v>
+        <v>0.097</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.145</v>
+        <v>0.144</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="23">
@@ -3944,7 +3944,7 @@
         <v>0.571</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.197</v>
+        <v>0.196</v>
       </c>
       <c r="AW23" t="n">
         <v>0.038</v>
@@ -4103,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.275</v>
+        <v>0.274</v>
       </c>
       <c r="AW24" t="n">
         <v>0</v>
@@ -4739,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.142</v>
+        <v>0.141</v>
       </c>
       <c r="AW28" t="n">
         <v>0.172</v>
@@ -4758,22 +4758,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C29" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E29" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H29" t="n">
         <v>7</v>
@@ -4782,13 +4782,13 @@
         <v>9</v>
       </c>
       <c r="J29" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="K29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M29" t="n">
         <v>6</v>
@@ -4800,25 +4800,25 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Q29" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="R29" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="S29" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T29" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="U29" t="n">
         <v>5</v>
       </c>
       <c r="V29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -4830,28 +4830,28 @@
         <v>11</v>
       </c>
       <c r="Z29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.478</v>
+        <v>0.458</v>
       </c>
       <c r="AB29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AC29" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.25</v>
+        <v>0.368</v>
       </c>
       <c r="AE29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF29" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.25</v>
+        <v>0.316</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
@@ -4863,51 +4863,51 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL29" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.267</v>
+        <v>0.289</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>269:19</t>
+          <t>304:07</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>114.96</v>
+        <v>133.96</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.308</v>
+        <v>0.36</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.336</v>
+        <v>0.382</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.478</v>
+        <v>0.552</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.287</v>
+        <v>0.276</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.09</v>
+        <v>0.075</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.818</v>
+        <v>1.919</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.187</v>
+        <v>0.192</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.078</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.067</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="30">
@@ -5057,7 +5057,7 @@
         <v>0.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.238</v>
+        <v>0.237</v>
       </c>
       <c r="AW30" t="n">
         <v>0.033</v>
@@ -5076,49 +5076,49 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>34</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>51</v>
+      </c>
+      <c r="L31" t="n">
+        <v>64</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
         <v>32</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>50</v>
-      </c>
-      <c r="L31" t="n">
-        <v>60</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>31</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5235,144 +5235,144 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C32" t="n">
-        <v>2751</v>
+        <v>2932</v>
       </c>
       <c r="D32" t="n">
+        <v>645</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1254</v>
+      </c>
+      <c r="F32" t="n">
+        <v>332</v>
+      </c>
+      <c r="G32" t="n">
+        <v>974</v>
+      </c>
+      <c r="H32" t="n">
+        <v>646</v>
+      </c>
+      <c r="I32" t="n">
+        <v>857</v>
+      </c>
+      <c r="J32" t="n">
         <v>601</v>
       </c>
-      <c r="E32" t="n">
-        <v>1177</v>
-      </c>
-      <c r="F32" t="n">
-        <v>315</v>
-      </c>
-      <c r="G32" t="n">
-        <v>909</v>
-      </c>
-      <c r="H32" t="n">
-        <v>604</v>
-      </c>
-      <c r="I32" t="n">
-        <v>798</v>
-      </c>
-      <c r="J32" t="n">
-        <v>570</v>
-      </c>
       <c r="K32" t="n">
-        <v>757</v>
+        <v>817</v>
       </c>
       <c r="L32" t="n">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="M32" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="N32" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>497</v>
+        <v>522</v>
       </c>
       <c r="Q32" t="n">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="R32" t="n">
-        <v>763</v>
+        <v>810</v>
       </c>
       <c r="S32" t="n">
-        <v>785</v>
+        <v>832</v>
       </c>
       <c r="T32" t="n">
-        <v>3015</v>
+        <v>3210</v>
       </c>
       <c r="U32" t="n">
-        <v>373</v>
+        <v>401</v>
       </c>
       <c r="V32" t="n">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="W32" t="n">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="X32" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="Y32" t="n">
-        <v>1005</v>
+        <v>1079</v>
       </c>
       <c r="Z32" t="n">
-        <v>1379</v>
+        <v>1484</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.729</v>
+        <v>0.727</v>
       </c>
       <c r="AB32" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AC32" t="n">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.344</v>
+        <v>0.348</v>
       </c>
       <c r="AE32" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AF32" t="n">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.321</v>
+        <v>0.322</v>
       </c>
       <c r="AH32" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="n">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.35</v>
+        <v>0.345</v>
       </c>
       <c r="AK32" t="n">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="AL32" t="n">
-        <v>669</v>
+        <v>719</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.345</v>
+        <v>0.339</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>6425:00</t>
+          <t>6825:00</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>2934.12</v>
+        <v>3127.08</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.515</v>
+        <v>0.513</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR32" t="n">
         <v>0.9379999999999999</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.169</v>
+        <v>0.167</v>
       </c>
       <c r="AT32" t="n">
         <v>0.29</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.147</v>
+        <v>1.151</v>
       </c>
       <c r="AV32" t="n">
         <v>0.2</v>
@@ -5381,7 +5381,7 @@
         <v>0.062</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.128</v>
+        <v>0.129</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
@@ -5394,150 +5394,150 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>2913</v>
+        <v>3080</v>
       </c>
       <c r="D33" t="n">
-        <v>739</v>
+        <v>787</v>
       </c>
       <c r="E33" t="n">
-        <v>1341</v>
+        <v>1421</v>
       </c>
       <c r="F33" t="n">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="G33" t="n">
-        <v>809</v>
+        <v>864</v>
       </c>
       <c r="H33" t="n">
-        <v>589</v>
+        <v>618</v>
       </c>
       <c r="I33" t="n">
-        <v>781</v>
+        <v>819</v>
       </c>
       <c r="J33" t="n">
-        <v>509</v>
+        <v>535</v>
       </c>
       <c r="K33" t="n">
-        <v>834</v>
+        <v>887</v>
       </c>
       <c r="L33" t="n">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="M33" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="N33" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>503</v>
+        <v>534</v>
       </c>
       <c r="Q33" t="n">
-        <v>467</v>
+        <v>493</v>
       </c>
       <c r="R33" t="n">
-        <v>794</v>
+        <v>847</v>
       </c>
       <c r="S33" t="n">
-        <v>755</v>
+        <v>803</v>
       </c>
       <c r="T33" t="n">
-        <v>3274</v>
+        <v>3440</v>
       </c>
       <c r="U33" t="n">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="V33" t="n">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="W33" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="X33" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Y33" t="n">
-        <v>1115</v>
+        <v>1170</v>
       </c>
       <c r="Z33" t="n">
-        <v>1561</v>
+        <v>1637</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.714</v>
+        <v>0.715</v>
       </c>
       <c r="AB33" t="n">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="AC33" t="n">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.382</v>
+        <v>0.392</v>
       </c>
       <c r="AE33" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="AF33" t="n">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.376</v>
+        <v>0.387</v>
       </c>
       <c r="AH33" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="AI33" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.406</v>
+        <v>0.392</v>
       </c>
       <c r="AK33" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="AL33" t="n">
-        <v>671</v>
+        <v>711</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.337</v>
+        <v>0.332</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>6425:00</t>
+          <t>6825:00</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>2996.64</v>
+        <v>3179.36</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.54</v>
+        <v>0.539</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.584</v>
+        <v>0.582</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.972</v>
+        <v>0.969</v>
       </c>
       <c r="AS33" t="n">
         <v>0.168</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.274</v>
+        <v>0.27</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.012</v>
+        <v>1.002</v>
       </c>
       <c r="AV33" t="n">
         <v>0.2</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX33" t="n">
         <v>0.138</v>
@@ -5610,16 +5610,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>4.781</v>
+        <v>4.794</v>
       </c>
       <c r="D35" t="n">
-        <v>1.812</v>
+        <v>1.824</v>
       </c>
       <c r="E35" t="n">
-        <v>2.062</v>
+        <v>2.059</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -5628,70 +5628,70 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.156</v>
+        <v>1.147</v>
       </c>
       <c r="I35" t="n">
-        <v>1.875</v>
+        <v>1.882</v>
       </c>
       <c r="J35" t="n">
-        <v>0.312</v>
+        <v>0.324</v>
       </c>
       <c r="K35" t="n">
-        <v>1.438</v>
+        <v>1.471</v>
       </c>
       <c r="L35" t="n">
-        <v>0.969</v>
+        <v>0.912</v>
       </c>
       <c r="M35" t="n">
-        <v>0.125</v>
+        <v>0.147</v>
       </c>
       <c r="N35" t="n">
-        <v>1.656</v>
+        <v>1.618</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.625</v>
+        <v>0.676</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.625</v>
+        <v>0.676</v>
       </c>
       <c r="R35" t="n">
-        <v>2.25</v>
+        <v>2.265</v>
       </c>
       <c r="S35" t="n">
-        <v>1.219</v>
+        <v>1.235</v>
       </c>
       <c r="T35" t="n">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="U35" t="n">
-        <v>0.625</v>
+        <v>0.647</v>
       </c>
       <c r="V35" t="n">
-        <v>0.719</v>
+        <v>0.735</v>
       </c>
       <c r="W35" t="n">
-        <v>0.062</v>
+        <v>0.176</v>
       </c>
       <c r="X35" t="n">
-        <v>0.031</v>
+        <v>0.118</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.969</v>
+        <v>2.971</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.844</v>
+        <v>3.853</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.772</v>
+        <v>0.771</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5700,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -5725,38 +5725,38 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>3.512</v>
+        <v>3.564</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.879</v>
+        <v>0.886</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.828</v>
+        <v>0.83</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.361</v>
+        <v>1.345</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.178</v>
+        <v>0.19</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.5</v>
+        <v>0.478</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.111</v>
+        <v>0.114</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.074</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.112</v>
+        <v>0.116</v>
       </c>
       <c r="AY35" t="n">
         <v>0.012</v>
@@ -5909,7 +5909,7 @@
         <v>2.31</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.27</v>
+        <v>0.269</v>
       </c>
       <c r="AW36" t="n">
         <v>0.041</v>
@@ -5918,7 +5918,7 @@
         <v>0.091</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.197</v>
+        <v>0.196</v>
       </c>
     </row>
     <row r="37">
@@ -5928,156 +5928,156 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>1.375</v>
+        <v>1.8</v>
       </c>
       <c r="E37" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="F37" t="n">
         <v>0.5</v>
       </c>
       <c r="G37" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="H37" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="J37" t="n">
-        <v>1.875</v>
+        <v>1.6</v>
       </c>
       <c r="K37" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="M37" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="N37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>75</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD37" t="n">
         <v>0.5</v>
       </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R37" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T37" t="n">
-        <v>46</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>3.625</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AE37" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="AG37" t="n">
         <v>0.4</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.625</v>
+        <v>1.4</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.154</v>
+        <v>0.214</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.625</v>
+        <v>1.4</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.154</v>
+        <v>0.143</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>9.289999999999999</v>
+        <v>9.692</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.354</v>
+        <v>0.411</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.464</v>
+        <v>0.507</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.753</v>
+        <v>0.846</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.188</v>
+        <v>0.165</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.458</v>
+        <v>0.5</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.071</v>
+        <v>1</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.236</v>
+        <v>0.253</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.077</v>
+        <v>0.101</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="38">
@@ -6246,156 +6246,156 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C39" t="n">
-        <v>10.455</v>
+        <v>10.333</v>
       </c>
       <c r="D39" t="n">
-        <v>1.409</v>
+        <v>1.333</v>
       </c>
       <c r="E39" t="n">
-        <v>3.455</v>
+        <v>3.417</v>
       </c>
       <c r="F39" t="n">
-        <v>2.045</v>
+        <v>2.042</v>
       </c>
       <c r="G39" t="n">
-        <v>5.909</v>
+        <v>6</v>
       </c>
       <c r="H39" t="n">
-        <v>1.5</v>
+        <v>1.542</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>2.083</v>
       </c>
       <c r="J39" t="n">
-        <v>6.227</v>
+        <v>5.917</v>
       </c>
       <c r="K39" t="n">
-        <v>1.182</v>
+        <v>1.125</v>
       </c>
       <c r="L39" t="n">
-        <v>0.409</v>
+        <v>0.417</v>
       </c>
       <c r="M39" t="n">
-        <v>1.045</v>
+        <v>0.958</v>
       </c>
       <c r="N39" t="n">
-        <v>0.227</v>
+        <v>0.25</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.636</v>
+        <v>2.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.636</v>
+        <v>2.5</v>
       </c>
       <c r="R39" t="n">
         <v>2.5</v>
       </c>
       <c r="S39" t="n">
-        <v>2.545</v>
+        <v>2.417</v>
       </c>
       <c r="T39" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="U39" t="n">
-        <v>1.364</v>
+        <v>1.5</v>
       </c>
       <c r="V39" t="n">
-        <v>1.409</v>
+        <v>1.292</v>
       </c>
       <c r="W39" t="n">
-        <v>0.864</v>
+        <v>0.917</v>
       </c>
       <c r="X39" t="n">
-        <v>0.409</v>
+        <v>0.417</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.136</v>
+        <v>2.125</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.455</v>
+        <v>3.458</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.618</v>
+        <v>0.614</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.636</v>
+        <v>0.625</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.545</v>
+        <v>1.542</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.412</v>
+        <v>0.405</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.136</v>
+        <v>0.125</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.455</v>
+        <v>0.5</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.364</v>
+        <v>0.333</v>
       </c>
       <c r="AI39" t="n">
-        <v>1</v>
+        <v>1.042</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.364</v>
+        <v>0.32</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.682</v>
+        <v>1.708</v>
       </c>
       <c r="AL39" t="n">
-        <v>4.909</v>
+        <v>4.958</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.343</v>
+        <v>0.345</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>21:25</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>12.88</v>
+        <v>12.833</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.478</v>
+        <v>0.467</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.805</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.205</v>
+        <v>0.195</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.16</v>
+        <v>0.164</v>
       </c>
       <c r="AU39" t="n">
-        <v>2.362</v>
+        <v>2.367</v>
       </c>
       <c r="AV39" t="n">
         <v>0.263</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.06</v>
+        <v>0.057</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.247</v>
+        <v>0.233</v>
       </c>
     </row>
     <row r="40">
@@ -6405,153 +6405,153 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C40" t="n">
-        <v>13.581</v>
+        <v>13.303</v>
       </c>
       <c r="D40" t="n">
-        <v>1.452</v>
+        <v>1.424</v>
       </c>
       <c r="E40" t="n">
-        <v>2.968</v>
+        <v>2.848</v>
       </c>
       <c r="F40" t="n">
-        <v>2.71</v>
+        <v>2.636</v>
       </c>
       <c r="G40" t="n">
-        <v>6.613</v>
+        <v>6.606</v>
       </c>
       <c r="H40" t="n">
-        <v>2.548</v>
+        <v>2.545</v>
       </c>
       <c r="I40" t="n">
-        <v>3.226</v>
+        <v>3.212</v>
       </c>
       <c r="J40" t="n">
-        <v>0.774</v>
+        <v>0.788</v>
       </c>
       <c r="K40" t="n">
-        <v>4.194</v>
+        <v>4.333</v>
       </c>
       <c r="L40" t="n">
-        <v>0.903</v>
+        <v>0.879</v>
       </c>
       <c r="M40" t="n">
-        <v>0.742</v>
+        <v>0.697</v>
       </c>
       <c r="N40" t="n">
-        <v>0.194</v>
+        <v>0.182</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.032</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.032</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>2.032</v>
+        <v>2</v>
       </c>
       <c r="S40" t="n">
-        <v>2.581</v>
+        <v>2.545</v>
       </c>
       <c r="T40" t="n">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="U40" t="n">
-        <v>2.129</v>
+        <v>2.182</v>
       </c>
       <c r="V40" t="n">
-        <v>1.677</v>
+        <v>1.667</v>
       </c>
       <c r="W40" t="n">
-        <v>1.129</v>
+        <v>1.091</v>
       </c>
       <c r="X40" t="n">
-        <v>0.645</v>
+        <v>0.636</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.419</v>
+        <v>3.424</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.419</v>
+        <v>4.394</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.774</v>
+        <v>0.779</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.258</v>
+        <v>0.242</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.71</v>
+        <v>0.667</v>
       </c>
       <c r="AD40" t="n">
         <v>0.364</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.323</v>
+        <v>0.303</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.065</v>
+        <v>1</v>
       </c>
       <c r="AG40" t="n">
         <v>0.303</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.581</v>
+        <v>0.545</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.581</v>
+        <v>1.545</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.367</v>
+        <v>0.353</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.129</v>
+        <v>2.091</v>
       </c>
       <c r="AL40" t="n">
-        <v>5.032</v>
+        <v>5.061</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.423</v>
+        <v>0.413</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>25:11</t>
+          <t>25:00</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>12.032</v>
+        <v>11.868</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.576</v>
+        <v>0.569</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.617</v>
+        <v>0.612</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.129</v>
+        <v>1.121</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.266</v>
+        <v>0.269</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.75</v>
+        <v>0.788</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.209</v>
+        <v>0.207</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.18</v>
+        <v>0.187</v>
       </c>
       <c r="AY40" t="n">
         <v>0.032</v>
@@ -6564,156 +6564,156 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C41" t="n">
-        <v>9.586</v>
+        <v>9.645</v>
       </c>
       <c r="D41" t="n">
-        <v>2.172</v>
+        <v>2.226</v>
       </c>
       <c r="E41" t="n">
-        <v>4.379</v>
+        <v>4.355</v>
       </c>
       <c r="F41" t="n">
-        <v>0.759</v>
+        <v>0.742</v>
       </c>
       <c r="G41" t="n">
-        <v>2.517</v>
+        <v>2.452</v>
       </c>
       <c r="H41" t="n">
-        <v>2.966</v>
+        <v>2.968</v>
       </c>
       <c r="I41" t="n">
-        <v>3.517</v>
+        <v>3.516</v>
       </c>
       <c r="J41" t="n">
-        <v>1.103</v>
+        <v>1.032</v>
       </c>
       <c r="K41" t="n">
-        <v>2.724</v>
+        <v>2.71</v>
       </c>
       <c r="L41" t="n">
-        <v>0.724</v>
+        <v>0.677</v>
       </c>
       <c r="M41" t="n">
-        <v>0.759</v>
+        <v>0.774</v>
       </c>
       <c r="N41" t="n">
-        <v>0.655</v>
+        <v>0.613</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.759</v>
+        <v>1.71</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.759</v>
+        <v>1.71</v>
       </c>
       <c r="R41" t="n">
-        <v>1.483</v>
+        <v>1.452</v>
       </c>
       <c r="S41" t="n">
-        <v>3.655</v>
+        <v>3.645</v>
       </c>
       <c r="T41" t="n">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="U41" t="n">
-        <v>1.414</v>
+        <v>1.484</v>
       </c>
       <c r="V41" t="n">
-        <v>1.069</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
-        <v>1.241</v>
+        <v>1.452</v>
       </c>
       <c r="X41" t="n">
-        <v>0.793</v>
+        <v>0.968</v>
       </c>
       <c r="Y41" t="n">
-        <v>4.414</v>
+        <v>4.484</v>
       </c>
       <c r="Z41" t="n">
-        <v>5.724</v>
+        <v>5.742</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.771</v>
+        <v>0.781</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.448</v>
+        <v>0.452</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.517</v>
+        <v>1.484</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.295</v>
+        <v>0.304</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.276</v>
+        <v>0.258</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.655</v>
+        <v>0.645</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.421</v>
+        <v>0.4</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.276</v>
+        <v>0.258</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.655</v>
+        <v>0.645</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.421</v>
+        <v>0.4</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.483</v>
+        <v>0.484</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.862</v>
+        <v>1.806</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.259</v>
+        <v>0.268</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>10.203</v>
+        <v>10.063</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.48</v>
+        <v>0.491</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.577</v>
       </c>
       <c r="AR41" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.958</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.172</v>
+        <v>0.17</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.43</v>
+        <v>0.436</v>
       </c>
       <c r="AU41" t="n">
-        <v>0.627</v>
+        <v>0.604</v>
       </c>
       <c r="AV41" t="n">
         <v>0.229</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.151</v>
+        <v>0.153</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="42">
@@ -6723,156 +6723,156 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C42" t="n">
-        <v>6.531</v>
+        <v>6.382</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.676</v>
       </c>
       <c r="E42" t="n">
-        <v>1.469</v>
+        <v>1.471</v>
       </c>
       <c r="F42" t="n">
+        <v>1.471</v>
+      </c>
+      <c r="G42" t="n">
+        <v>4.206</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.529</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.059</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="T42" t="n">
+        <v>160</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="Z42" t="n">
         <v>1.5</v>
       </c>
-      <c r="G42" t="n">
-        <v>4.188</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.656</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1.531</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.906</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="R42" t="n">
-        <v>2.062</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="T42" t="n">
-        <v>159</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.188</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.062</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.531</v>
-      </c>
       <c r="AA42" t="n">
-        <v>0.694</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="AC42" t="n">
         <v>0.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.312</v>
+        <v>0.294</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.281</v>
+        <v>0.265</v>
       </c>
       <c r="AG42" t="n">
         <v>0.444</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.588</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.625</v>
+        <v>1.647</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.346</v>
+        <v>0.357</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.882</v>
       </c>
       <c r="AL42" t="n">
-        <v>2.562</v>
+        <v>2.559</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.366</v>
+        <v>0.345</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>6.559</v>
+        <v>6.614</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.519</v>
+        <v>0.508</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.542</v>
+        <v>0.53</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.996</v>
+        <v>0.965</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.081</v>
+        <v>0.089</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.116</v>
+        <v>0.109</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.471</v>
+        <v>1.25</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.141</v>
+        <v>0.143</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.047</v>
+        <v>0.046</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.081</v>
+        <v>0.082</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="43">
@@ -6882,156 +6882,156 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="D43" t="n">
-        <v>1.107</v>
+        <v>1.033</v>
       </c>
       <c r="E43" t="n">
-        <v>1.929</v>
+        <v>1.833</v>
       </c>
       <c r="F43" t="n">
-        <v>0.143</v>
+        <v>0.133</v>
       </c>
       <c r="G43" t="n">
-        <v>0.786</v>
+        <v>0.867</v>
       </c>
       <c r="H43" t="n">
-        <v>0.357</v>
+        <v>0.333</v>
       </c>
       <c r="I43" t="n">
-        <v>0.607</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>0.393</v>
+        <v>0.367</v>
       </c>
       <c r="K43" t="n">
-        <v>1.679</v>
+        <v>1.867</v>
       </c>
       <c r="L43" t="n">
-        <v>0.607</v>
+        <v>0.633</v>
       </c>
       <c r="M43" t="n">
-        <v>0.643</v>
+        <v>0.6</v>
       </c>
       <c r="N43" t="n">
-        <v>0.643</v>
+        <v>0.6</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.607</v>
+        <v>0.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.607</v>
+        <v>0.6</v>
       </c>
       <c r="R43" t="n">
-        <v>1.321</v>
+        <v>1.367</v>
       </c>
       <c r="S43" t="n">
-        <v>0.464</v>
+        <v>0.467</v>
       </c>
       <c r="T43" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="U43" t="n">
-        <v>0.464</v>
+        <v>0.433</v>
       </c>
       <c r="V43" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="W43" t="n">
-        <v>0.286</v>
+        <v>0.267</v>
       </c>
       <c r="X43" t="n">
-        <v>0.179</v>
+        <v>0.167</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.214</v>
+        <v>1.133</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.857</v>
+        <v>1.767</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.654</v>
+        <v>0.642</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.179</v>
+        <v>0.167</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.571</v>
+        <v>0.533</v>
       </c>
       <c r="AD43" t="n">
         <v>0.312</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.067</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="AG43" t="n">
         <v>0.667</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.464</v>
+        <v>0.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.077</v>
+        <v>0.067</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.321</v>
+        <v>0.367</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>3.589</v>
+        <v>3.549</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.487</v>
+        <v>0.457</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.503</v>
+        <v>0.475</v>
       </c>
       <c r="AR43" t="n">
-        <v>0.836</v>
+        <v>0.789</v>
       </c>
       <c r="AS43" t="n">
         <v>0.169</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.132</v>
+        <v>0.123</v>
       </c>
       <c r="AU43" t="n">
-        <v>0.647</v>
+        <v>0.611</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.132</v>
+        <v>0.126</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.054</v>
+        <v>0.055</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.153</v>
+        <v>0.165</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="44">
@@ -7200,16 +7200,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C45" t="n">
-        <v>1.462</v>
+        <v>1.4</v>
       </c>
       <c r="D45" t="n">
-        <v>0.462</v>
+        <v>0.467</v>
       </c>
       <c r="E45" t="n">
-        <v>0.923</v>
+        <v>0.867</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -7218,49 +7218,49 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.538</v>
+        <v>0.467</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0.867</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0.385</v>
+        <v>0.4</v>
       </c>
       <c r="L45" t="n">
-        <v>0.385</v>
+        <v>0.333</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="N45" t="n">
-        <v>0.538</v>
+        <v>0.467</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.462</v>
+        <v>0.6</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.462</v>
+        <v>0.6</v>
       </c>
       <c r="R45" t="n">
-        <v>0.923</v>
+        <v>0.867</v>
       </c>
       <c r="S45" t="n">
-        <v>0.538</v>
+        <v>0.467</v>
       </c>
       <c r="T45" t="n">
         <v>13</v>
       </c>
       <c r="U45" t="n">
-        <v>0.077</v>
+        <v>0.067</v>
       </c>
       <c r="V45" t="n">
-        <v>0.615</v>
+        <v>0.533</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -7269,19 +7269,19 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.923</v>
+        <v>0.867</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.462</v>
+        <v>1.333</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.632</v>
+        <v>0.65</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.077</v>
+        <v>0.067</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.462</v>
+        <v>0.4</v>
       </c>
       <c r="AD45" t="n">
         <v>0.167</v>
@@ -7315,38 +7315,38 @@
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>04:24</t>
+          <t>04:27</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>1.825</v>
+        <v>1.848</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.5</v>
+        <v>0.538</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.536</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.801</v>
+        <v>0.758</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.253</v>
+        <v>0.325</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.583</v>
+        <v>0.538</v>
       </c>
       <c r="AU45" t="n">
         <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.182</v>
+        <v>0.181</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.093</v>
+        <v>0.079</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.095</v>
+        <v>0.097</v>
       </c>
       <c r="AY45" t="n">
         <v>0</v>
@@ -7359,156 +7359,156 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C46" t="n">
-        <v>9</v>
+        <v>8.882</v>
       </c>
       <c r="D46" t="n">
-        <v>2.067</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>4.133</v>
+        <v>4.059</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>2.733</v>
+        <v>2.765</v>
       </c>
       <c r="H46" t="n">
-        <v>2.067</v>
+        <v>2.059</v>
       </c>
       <c r="I46" t="n">
-        <v>2.533</v>
+        <v>2.588</v>
       </c>
       <c r="J46" t="n">
-        <v>2.933</v>
+        <v>2.882</v>
       </c>
       <c r="K46" t="n">
-        <v>1.933</v>
+        <v>1.882</v>
       </c>
       <c r="L46" t="n">
-        <v>0.733</v>
+        <v>0.765</v>
       </c>
       <c r="M46" t="n">
-        <v>1.133</v>
+        <v>1.118</v>
       </c>
       <c r="N46" t="n">
-        <v>0.2</v>
+        <v>0.176</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.667</v>
+        <v>1.529</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.667</v>
+        <v>1.529</v>
       </c>
       <c r="R46" t="n">
-        <v>1.933</v>
+        <v>2.059</v>
       </c>
       <c r="S46" t="n">
-        <v>2.333</v>
+        <v>2.412</v>
       </c>
       <c r="T46" t="n">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="U46" t="n">
-        <v>1.467</v>
+        <v>1.294</v>
       </c>
       <c r="V46" t="n">
-        <v>1.067</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="W46" t="n">
-        <v>0.467</v>
+        <v>0.588</v>
       </c>
       <c r="X46" t="n">
-        <v>0.4</v>
+        <v>0.412</v>
       </c>
       <c r="Y46" t="n">
-        <v>3.133</v>
+        <v>3.176</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.133</v>
+        <v>4.294</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.758</v>
+        <v>0.74</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.733</v>
+        <v>0.647</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.667</v>
+        <v>1.529</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.44</v>
+        <v>0.423</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.267</v>
+        <v>0.235</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.867</v>
+        <v>0.824</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.308</v>
+        <v>0.286</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.2</v>
+        <v>0.235</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.6</v>
+        <v>0.647</v>
       </c>
       <c r="AJ46" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>2.118</v>
+      </c>
+      <c r="AM46" t="n">
         <v>0.333</v>
       </c>
-      <c r="AK46" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>2.133</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>0.344</v>
-      </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>9.648</v>
+        <v>9.492000000000001</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.505</v>
+        <v>0.5</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AR46" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.173</v>
+        <v>0.161</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.301</v>
+        <v>0.302</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.76</v>
+        <v>1.885</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.038</v>
+        <v>0.04</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.103</v>
+        <v>0.101</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.114</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="47">
@@ -7518,156 +7518,156 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C47" t="n">
-        <v>8.880000000000001</v>
+        <v>8.815</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>2.037</v>
       </c>
       <c r="E47" t="n">
-        <v>3.16</v>
+        <v>3.185</v>
       </c>
       <c r="F47" t="n">
-        <v>0.48</v>
+        <v>0.444</v>
       </c>
       <c r="G47" t="n">
-        <v>1.36</v>
+        <v>1.333</v>
       </c>
       <c r="H47" t="n">
-        <v>3.44</v>
+        <v>3.407</v>
       </c>
       <c r="I47" t="n">
-        <v>3.88</v>
+        <v>3.889</v>
       </c>
       <c r="J47" t="n">
-        <v>1.36</v>
+        <v>1.407</v>
       </c>
       <c r="K47" t="n">
-        <v>3.6</v>
+        <v>3.778</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>2.111</v>
       </c>
       <c r="M47" t="n">
-        <v>0.16</v>
+        <v>0.148</v>
       </c>
       <c r="N47" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.16</v>
+        <v>1.074</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.16</v>
+        <v>1.074</v>
       </c>
       <c r="R47" t="n">
-        <v>2.8</v>
+        <v>2.778</v>
       </c>
       <c r="S47" t="n">
-        <v>3.16</v>
+        <v>3.074</v>
       </c>
       <c r="T47" t="n">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="U47" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.593</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>4.741</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="AC47" t="n">
         <v>1</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0.848</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.08</v>
       </c>
       <c r="AD47" t="n">
         <v>0.519</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.2</v>
+        <v>0.185</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.44</v>
+        <v>0.407</v>
       </c>
       <c r="AG47" t="n">
         <v>0.455</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.04</v>
+        <v>0.037</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.16</v>
+        <v>0.148</v>
       </c>
       <c r="AJ47" t="n">
         <v>0.25</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.44</v>
+        <v>0.407</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.2</v>
+        <v>1.185</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.367</v>
+        <v>0.344</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>7.387</v>
+        <v>7.304</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.602</v>
+        <v>0.598</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.713</v>
+        <v>0.707</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.202</v>
+        <v>1.207</v>
       </c>
       <c r="AS47" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AV47" t="n">
         <v>0.157</v>
       </c>
-      <c r="AT47" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>1.172</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>0.161</v>
-      </c>
       <c r="AW47" t="n">
-        <v>0.106</v>
+        <v>0.11</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.194</v>
+        <v>0.202</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.052</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="48">
@@ -7677,156 +7677,156 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C48" t="n">
-        <v>12.214</v>
+        <v>12.3</v>
       </c>
       <c r="D48" t="n">
-        <v>3.25</v>
+        <v>3.333</v>
       </c>
       <c r="E48" t="n">
-        <v>6.179</v>
+        <v>6.4</v>
       </c>
       <c r="F48" t="n">
-        <v>0.607</v>
+        <v>0.6</v>
       </c>
       <c r="G48" t="n">
-        <v>2.179</v>
+        <v>2.167</v>
       </c>
       <c r="H48" t="n">
-        <v>3.893</v>
+        <v>3.833</v>
       </c>
       <c r="I48" t="n">
-        <v>5.393</v>
+        <v>5.267</v>
       </c>
       <c r="J48" t="n">
+        <v>1.933</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R48" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="T48" t="n">
+        <v>370</v>
+      </c>
+      <c r="U48" t="n">
         <v>2</v>
       </c>
-      <c r="K48" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="M48" t="n">
-        <v>1.214</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.286</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>2.286</v>
-      </c>
-      <c r="R48" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="S48" t="n">
-        <v>5.643</v>
-      </c>
-      <c r="T48" t="n">
-        <v>341</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.893</v>
-      </c>
       <c r="V48" t="n">
-        <v>1.214</v>
+        <v>1.133</v>
       </c>
       <c r="W48" t="n">
-        <v>1.464</v>
+        <v>1.5</v>
       </c>
       <c r="X48" t="n">
-        <v>0.964</v>
+        <v>0.967</v>
       </c>
       <c r="Y48" t="n">
-        <v>6.5</v>
+        <v>6.467</v>
       </c>
       <c r="Z48" t="n">
-        <v>8.893000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.731</v>
+        <v>0.735</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.429</v>
+        <v>0.467</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.714</v>
+        <v>1.9</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.25</v>
+        <v>0.246</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.214</v>
+        <v>0.233</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.964</v>
+        <v>0.967</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.222</v>
+        <v>0.241</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.5</v>
+        <v>0.467</v>
       </c>
       <c r="AJ48" t="n">
         <v>0.429</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.393</v>
+        <v>0.4</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.679</v>
+        <v>1.7</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.234</v>
+        <v>0.235</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>13.016</v>
+        <v>13.084</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.498</v>
+        <v>0.494</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.569</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.176</v>
+        <v>0.168</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.466</v>
+        <v>0.447</v>
       </c>
       <c r="AU48" t="n">
-        <v>0.875</v>
+        <v>0.879</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.266</v>
+        <v>0.268</v>
       </c>
       <c r="AW48" t="n">
         <v>0.023</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.081</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="49">
@@ -7976,16 +7976,16 @@
         <v>0.846</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.251</v>
+        <v>0.25</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.098</v>
+        <v>0.097</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.145</v>
+        <v>0.144</v>
       </c>
       <c r="AY49" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="50">
@@ -8135,7 +8135,7 @@
         <v>0.571</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.197</v>
+        <v>0.196</v>
       </c>
       <c r="AW50" t="n">
         <v>0.038</v>
@@ -8294,7 +8294,7 @@
         <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.275</v>
+        <v>0.274</v>
       </c>
       <c r="AW51" t="n">
         <v>0</v>
@@ -8930,7 +8930,7 @@
         <v>0</v>
       </c>
       <c r="AV55" t="n">
-        <v>0.142</v>
+        <v>0.141</v>
       </c>
       <c r="AW55" t="n">
         <v>0.172</v>
@@ -8949,156 +8949,156 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C56" t="n">
-        <v>2.895</v>
+        <v>3.524</v>
       </c>
       <c r="D56" t="n">
-        <v>0.632</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>2.421</v>
+        <v>2.524</v>
       </c>
       <c r="F56" t="n">
-        <v>0.421</v>
+        <v>0.524</v>
       </c>
       <c r="G56" t="n">
-        <v>1.684</v>
+        <v>1.905</v>
       </c>
       <c r="H56" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3.381</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1.762</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1.762</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1.524</v>
+      </c>
+      <c r="T56" t="n">
+        <v>75</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="AD56" t="n">
         <v>0.368</v>
       </c>
-      <c r="I56" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="J56" t="n">
-        <v>3.158</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1.105</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="M56" t="n">
+      <c r="AE56" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="AG56" t="n">
         <v>0.316</v>
       </c>
-      <c r="N56" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1.737</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>1.737</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.579</v>
-      </c>
-      <c r="S56" t="n">
-        <v>1.579</v>
-      </c>
-      <c r="T56" t="n">
-        <v>58</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>1.211</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0.478</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AH56" t="n">
         <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.105</v>
+        <v>0.095</v>
       </c>
       <c r="AJ56" t="n">
         <v>0</v>
       </c>
       <c r="AK56" t="n">
-        <v>0.421</v>
+        <v>0.524</v>
       </c>
       <c r="AL56" t="n">
-        <v>1.579</v>
+        <v>1.81</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.267</v>
+        <v>0.289</v>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AO56" t="n">
-        <v>6.051</v>
+        <v>6.379</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.308</v>
+        <v>0.36</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.336</v>
+        <v>0.382</v>
       </c>
       <c r="AR56" t="n">
-        <v>0.478</v>
+        <v>0.552</v>
       </c>
       <c r="AS56" t="n">
-        <v>0.287</v>
+        <v>0.276</v>
       </c>
       <c r="AT56" t="n">
-        <v>0.09</v>
+        <v>0.075</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.818</v>
+        <v>1.919</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.187</v>
+        <v>0.192</v>
       </c>
       <c r="AW56" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="AX56" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.078</v>
       </c>
       <c r="AY56" t="n">
-        <v>0.115</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="57">
@@ -9248,7 +9248,7 @@
         <v>0.2</v>
       </c>
       <c r="AV57" t="n">
-        <v>0.238</v>
+        <v>0.237</v>
       </c>
       <c r="AW57" t="n">
         <v>0.033</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -9294,10 +9294,10 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1.562</v>
+        <v>1.5</v>
       </c>
       <c r="L58" t="n">
-        <v>1.875</v>
+        <v>1.882</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -9309,13 +9309,13 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0.969</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -9426,144 +9426,144 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C59" t="n">
-        <v>85.96899999999999</v>
+        <v>86.235</v>
       </c>
       <c r="D59" t="n">
-        <v>18.781</v>
+        <v>18.971</v>
       </c>
       <c r="E59" t="n">
-        <v>36.781</v>
+        <v>36.882</v>
       </c>
       <c r="F59" t="n">
-        <v>9.843999999999999</v>
+        <v>9.765000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>28.406</v>
+        <v>28.647</v>
       </c>
       <c r="H59" t="n">
-        <v>18.875</v>
+        <v>19</v>
       </c>
       <c r="I59" t="n">
-        <v>24.938</v>
+        <v>25.206</v>
       </c>
       <c r="J59" t="n">
-        <v>17.812</v>
+        <v>17.676</v>
       </c>
       <c r="K59" t="n">
-        <v>23.656</v>
+        <v>24.029</v>
       </c>
       <c r="L59" t="n">
-        <v>11.719</v>
+        <v>11.794</v>
       </c>
       <c r="M59" t="n">
-        <v>6.562</v>
+        <v>6.529</v>
       </c>
       <c r="N59" t="n">
-        <v>5.969</v>
+        <v>5.853</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>15.531</v>
+        <v>15.353</v>
       </c>
       <c r="Q59" t="n">
-        <v>14.562</v>
+        <v>14.412</v>
       </c>
       <c r="R59" t="n">
-        <v>23.844</v>
+        <v>23.824</v>
       </c>
       <c r="S59" t="n">
-        <v>24.531</v>
+        <v>24.471</v>
       </c>
       <c r="T59" t="n">
-        <v>3015</v>
+        <v>3210</v>
       </c>
       <c r="U59" t="n">
-        <v>11.656</v>
+        <v>11.794</v>
       </c>
       <c r="V59" t="n">
-        <v>11.938</v>
+        <v>12.029</v>
       </c>
       <c r="W59" t="n">
-        <v>7.469</v>
+        <v>7.882</v>
       </c>
       <c r="X59" t="n">
-        <v>4.562</v>
+        <v>4.853</v>
       </c>
       <c r="Y59" t="n">
-        <v>31.406</v>
+        <v>31.735</v>
       </c>
       <c r="Z59" t="n">
-        <v>43.094</v>
+        <v>43.647</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.729</v>
+        <v>0.727</v>
       </c>
       <c r="AB59" t="n">
-        <v>4.062</v>
+        <v>4.088</v>
       </c>
       <c r="AC59" t="n">
-        <v>11.812</v>
+        <v>11.765</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.344</v>
+        <v>0.348</v>
       </c>
       <c r="AE59" t="n">
-        <v>2.188</v>
+        <v>2.147</v>
       </c>
       <c r="AF59" t="n">
-        <v>6.812</v>
+        <v>6.676</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.321</v>
+        <v>0.322</v>
       </c>
       <c r="AH59" t="n">
-        <v>2.625</v>
+        <v>2.588</v>
       </c>
       <c r="AI59" t="n">
         <v>7.5</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.35</v>
+        <v>0.345</v>
       </c>
       <c r="AK59" t="n">
-        <v>7.219</v>
+        <v>7.176</v>
       </c>
       <c r="AL59" t="n">
-        <v>20.906</v>
+        <v>21.147</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.345</v>
+        <v>0.339</v>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>200:46</t>
+          <t>200:44</t>
         </is>
       </c>
       <c r="AO59" t="n">
-        <v>91.691</v>
+        <v>91.973</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.515</v>
+        <v>0.513</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR59" t="n">
         <v>0.9379999999999999</v>
       </c>
       <c r="AS59" t="n">
-        <v>0.169</v>
+        <v>0.167</v>
       </c>
       <c r="AT59" t="n">
         <v>0.29</v>
       </c>
       <c r="AU59" t="n">
-        <v>1.147</v>
+        <v>1.151</v>
       </c>
       <c r="AV59" t="n">
         <v>0.2</v>
@@ -9572,7 +9572,7 @@
         <v>0.062</v>
       </c>
       <c r="AX59" t="n">
-        <v>0.128</v>
+        <v>0.129</v>
       </c>
       <c r="AY59" t="n">
         <v>0</v>
@@ -9585,153 +9585,153 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C60" t="n">
-        <v>91.03100000000001</v>
+        <v>90.58799999999999</v>
       </c>
       <c r="D60" t="n">
-        <v>23.094</v>
+        <v>23.147</v>
       </c>
       <c r="E60" t="n">
-        <v>41.906</v>
+        <v>41.794</v>
       </c>
       <c r="F60" t="n">
-        <v>8.811999999999999</v>
+        <v>8.706</v>
       </c>
       <c r="G60" t="n">
-        <v>25.281</v>
+        <v>25.412</v>
       </c>
       <c r="H60" t="n">
-        <v>18.406</v>
+        <v>18.176</v>
       </c>
       <c r="I60" t="n">
-        <v>24.406</v>
+        <v>24.088</v>
       </c>
       <c r="J60" t="n">
-        <v>15.906</v>
+        <v>15.735</v>
       </c>
       <c r="K60" t="n">
-        <v>26.062</v>
+        <v>26.088</v>
       </c>
       <c r="L60" t="n">
-        <v>13.438</v>
+        <v>13.118</v>
       </c>
       <c r="M60" t="n">
-        <v>8.25</v>
+        <v>8.176</v>
       </c>
       <c r="N60" t="n">
-        <v>5.844</v>
+        <v>5.735</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>15.719</v>
+        <v>15.706</v>
       </c>
       <c r="Q60" t="n">
-        <v>14.594</v>
+        <v>14.5</v>
       </c>
       <c r="R60" t="n">
-        <v>24.812</v>
+        <v>24.912</v>
       </c>
       <c r="S60" t="n">
-        <v>23.594</v>
+        <v>23.618</v>
       </c>
       <c r="T60" t="n">
-        <v>3274</v>
+        <v>3440</v>
       </c>
       <c r="U60" t="n">
-        <v>11.906</v>
+        <v>11.853</v>
       </c>
       <c r="V60" t="n">
-        <v>13.188</v>
+        <v>12.824</v>
       </c>
       <c r="W60" t="n">
-        <v>5.688</v>
+        <v>5.559</v>
       </c>
       <c r="X60" t="n">
-        <v>3.562</v>
+        <v>3.471</v>
       </c>
       <c r="Y60" t="n">
-        <v>34.844</v>
+        <v>34.412</v>
       </c>
       <c r="Z60" t="n">
-        <v>48.781</v>
+        <v>48.147</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.714</v>
+        <v>0.715</v>
       </c>
       <c r="AB60" t="n">
-        <v>4</v>
+        <v>4.206</v>
       </c>
       <c r="AC60" t="n">
-        <v>10.469</v>
+        <v>10.735</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.382</v>
+        <v>0.392</v>
       </c>
       <c r="AE60" t="n">
-        <v>2.656</v>
+        <v>2.706</v>
       </c>
       <c r="AF60" t="n">
-        <v>7.062</v>
+        <v>7</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.376</v>
+        <v>0.387</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.75</v>
+        <v>1.765</v>
       </c>
       <c r="AI60" t="n">
-        <v>4.312</v>
+        <v>4.5</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.406</v>
+        <v>0.392</v>
       </c>
       <c r="AK60" t="n">
-        <v>7.062</v>
+        <v>6.941</v>
       </c>
       <c r="AL60" t="n">
-        <v>20.969</v>
+        <v>20.912</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.337</v>
+        <v>0.332</v>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>200:46</t>
+          <t>200:44</t>
         </is>
       </c>
       <c r="AO60" t="n">
-        <v>93.645</v>
+        <v>93.511</v>
       </c>
       <c r="AP60" t="n">
-        <v>0.54</v>
+        <v>0.539</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.584</v>
+        <v>0.582</v>
       </c>
       <c r="AR60" t="n">
-        <v>0.972</v>
+        <v>0.969</v>
       </c>
       <c r="AS60" t="n">
         <v>0.168</v>
       </c>
       <c r="AT60" t="n">
-        <v>0.274</v>
+        <v>0.27</v>
       </c>
       <c r="AU60" t="n">
-        <v>1.012</v>
+        <v>1.002</v>
       </c>
       <c r="AV60" t="n">
-        <v>0.204</v>
+        <v>0.203</v>
       </c>
       <c r="AW60" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AX60" t="n">
-        <v>0.141</v>
+        <v>0.14</v>
       </c>
       <c r="AY60" t="n">
         <v>0</v>
